--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetail.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetail.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="91">
   <si>
     <t>sku</t>
   </si>
@@ -40,15 +40,12 @@
     <t>品名</t>
   </si>
   <si>
-    <t>属性</t>
+    <t>产品属性</t>
   </si>
   <si>
     <t>品牌</t>
   </si>
   <si>
-    <t>产品属性</t>
-  </si>
-  <si>
     <t>计划上市时间</t>
   </si>
   <si>
@@ -182,9 +179,6 @@
   </si>
   <si>
     <t>{.brandName}</t>
-  </si>
-  <si>
-    <t>{.variantProperty}</t>
   </si>
   <si>
     <t>{.planListingTime}</t>
@@ -1273,29 +1267,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AU2"/>
+  <dimension ref="A1:AT2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="15" max="15" width="11.5" customWidth="1"/>
-    <col min="16" max="16" width="13" customWidth="1"/>
-    <col min="17" max="17" width="11" customWidth="1"/>
-    <col min="18" max="18" width="13.25" customWidth="1"/>
-    <col min="19" max="19" width="9.625" customWidth="1"/>
-    <col min="20" max="20" width="9.375" customWidth="1"/>
-    <col min="21" max="21" width="16" customWidth="1"/>
-    <col min="22" max="22" width="14.875" customWidth="1"/>
-    <col min="23" max="23" width="12" customWidth="1"/>
-    <col min="24" max="24" width="12.375" customWidth="1"/>
-    <col min="25" max="25" width="12.125" customWidth="1"/>
-    <col min="26" max="26" width="12.25" customWidth="1"/>
-    <col min="30" max="30" width="12.25" customWidth="1"/>
-    <col min="31" max="31" width="11.125" customWidth="1"/>
-    <col min="32" max="33" width="8.125" customWidth="1"/>
-    <col min="34" max="35" width="9.25" customWidth="1"/>
-    <col min="36" max="36" width="10.875" customWidth="1"/>
+    <col min="14" max="14" width="11.5" customWidth="1"/>
+    <col min="15" max="15" width="13" customWidth="1"/>
+    <col min="16" max="16" width="11" customWidth="1"/>
+    <col min="17" max="17" width="13.25" customWidth="1"/>
+    <col min="18" max="18" width="9.625" customWidth="1"/>
+    <col min="19" max="19" width="9.375" customWidth="1"/>
+    <col min="20" max="20" width="16" customWidth="1"/>
+    <col min="21" max="21" width="14.875" customWidth="1"/>
+    <col min="22" max="22" width="12" customWidth="1"/>
+    <col min="23" max="23" width="12.375" customWidth="1"/>
+    <col min="24" max="24" width="12.125" customWidth="1"/>
+    <col min="25" max="25" width="12.25" customWidth="1"/>
+    <col min="29" max="29" width="12.25" customWidth="1"/>
+    <col min="30" max="30" width="11.125" customWidth="1"/>
+    <col min="31" max="32" width="8.125" customWidth="1"/>
+    <col min="33" max="34" width="9.25" customWidth="1"/>
+    <col min="35" max="35" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47">
+    <row r="1" customFormat="1" spans="1:46">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1390,10 +1384,10 @@
         <v>30</v>
       </c>
       <c r="AF1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG1" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="AH1" s="1" t="s">
         <v>32</v>
@@ -1431,154 +1425,148 @@
       <c r="AS1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AT1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AU1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:46">
+      <c r="A2" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="2" spans="1:47">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="U2" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="V2" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="W2" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="X2" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="X2" s="1" t="s">
+      <c r="Y2" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="Z2" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="Z2" s="1" t="s">
+      <c r="AA2" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="AA2" s="1" t="s">
+      <c r="AB2" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="AB2" s="1" t="s">
+      <c r="AC2" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="AC2" s="1" t="s">
+      <c r="AD2" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="AD2" s="1" t="s">
+      <c r="AE2" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="AE2" s="1" t="s">
+      <c r="AF2" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="AF2" s="1" t="s">
+      <c r="AG2" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="AG2" s="1" t="s">
+      <c r="AH2" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="AH2" s="1" t="s">
+      <c r="AI2" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="AI2" s="1" t="s">
+      <c r="AJ2" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="AJ2" s="1" t="s">
+      <c r="AK2" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="AK2" s="1" t="s">
+      <c r="AL2" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="AL2" s="1" t="s">
+      <c r="AM2" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="AM2" s="1" t="s">
+      <c r="AN2" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="AN2" s="1" t="s">
+      <c r="AO2" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="AO2" s="1" t="s">
+      <c r="AP2" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="AP2" s="1" t="s">
+      <c r="AQ2" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="AQ2" s="1" t="s">
+      <c r="AR2" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="AR2" s="1" t="s">
+      <c r="AS2" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="AS2" s="1" t="s">
+      <c r="AT2" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="AT2" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="AU2" s="1" t="s">
-        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetail.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetail.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="92">
   <si>
     <t>sku</t>
   </si>
@@ -107,6 +107,9 @@
   </si>
   <si>
     <t>销售状态</t>
+  </si>
+  <si>
+    <t>报关产品属性</t>
   </si>
   <si>
     <t>报关中文名</t>
@@ -293,11 +296,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -938,11 +942,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1384,192 +1391,218 @@
         <v>30</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AT1" s="2" t="s">
         <v>44</v>
+      </c>
+      <c r="AT1" s="3" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:46">
       <c r="A2" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="K2" s="1" t="s">
         <v>55</v>
       </c>
+      <c r="K2" s="2" t="s">
+        <v>56</v>
+      </c>
       <c r="L2" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="AA2" s="1" t="s">
         <v>71</v>
       </c>
+      <c r="AA2" s="2" t="s">
+        <v>72</v>
+      </c>
       <c r="AB2" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AD2" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AE2" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF2" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG2" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH2" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AJ2" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AK2" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL2" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AM2" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AN2" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AO2" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AP2" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AQ2" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AR2" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AS2" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AT2" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="6">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2 AA2 AB2">
+      <formula1>32874</formula1>
+      <formula2>2958101</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:U2">
+      <formula1>0</formula1>
+      <formula2>999999999999</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2 X2 AS2">
+      <formula1>0</formula1>
+      <formula2>9999999999</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AP2">
+      <formula1>0</formula1>
+      <formula2>99999999999</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2 Y2 AR2">
+      <formula1>0</formula1>
+      <formula2>9999999999</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AO2">
+      <formula1>0</formula1>
+      <formula2>9999999999999</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetail.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetail.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="114">
   <si>
     <t>sku</t>
   </si>
@@ -40,12 +40,12 @@
     <t>品名</t>
   </si>
   <si>
+    <t>品牌</t>
+  </si>
+  <si>
     <t>产品属性</t>
   </si>
   <si>
-    <t>品牌</t>
-  </si>
-  <si>
     <t>计划上市时间</t>
   </si>
   <si>
@@ -151,6 +151,39 @@
     <t>单箱数量</t>
   </si>
   <si>
+    <t>ean码</t>
+  </si>
+  <si>
+    <t>计划首批下单量</t>
+  </si>
+  <si>
+    <t>首批下单时间</t>
+  </si>
+  <si>
+    <t>MOQ(最小起订量)</t>
+  </si>
+  <si>
+    <t>交货周期(天)</t>
+  </si>
+  <si>
+    <t>实际首批到货时间</t>
+  </si>
+  <si>
+    <t>实际首批到货量</t>
+  </si>
+  <si>
+    <t>首批到货状态</t>
+  </si>
+  <si>
+    <t>采购员</t>
+  </si>
+  <si>
+    <t>一级供应商</t>
+  </si>
+  <si>
+    <t>二级供应商</t>
+  </si>
+  <si>
     <t>错误信息</t>
   </si>
   <si>
@@ -178,12 +211,12 @@
     <t>{.name}</t>
   </si>
   <si>
+    <t>{.brandName}</t>
+  </si>
+  <si>
     <t>{.property}</t>
   </si>
   <si>
-    <t>{.brandName}</t>
-  </si>
-  <si>
     <t>{.planListingTime}</t>
   </si>
   <si>
@@ -287,6 +320,39 @@
   </si>
   <si>
     <t>{.boxQty}</t>
+  </si>
+  <si>
+    <t>{.ean}</t>
+  </si>
+  <si>
+    <t>{.planOrderQty}</t>
+  </si>
+  <si>
+    <t>{.placeOrderTime}</t>
+  </si>
+  <si>
+    <t>{.moq}</t>
+  </si>
+  <si>
+    <t>{.deliveryCycle}</t>
+  </si>
+  <si>
+    <t>{.actualArrivalTime}</t>
+  </si>
+  <si>
+    <t>{.actualArrivalQty}</t>
+  </si>
+  <si>
+    <t>{.arrivalState}</t>
+  </si>
+  <si>
+    <t>{.purchaseUser}</t>
+  </si>
+  <si>
+    <t>{.mainSupplier}</t>
+  </si>
+  <si>
+    <t>{.secondSupplier}</t>
   </si>
   <si>
     <t>{.errorMsg}</t>
@@ -942,7 +1008,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -950,6 +1016,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1274,8 +1343,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AT2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
+  <dimension ref="A1:BE6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
   <cols>
     <col min="14" max="14" width="11.5" customWidth="1"/>
     <col min="15" max="15" width="13" customWidth="1"/>
@@ -1294,9 +1363,20 @@
     <col min="31" max="32" width="8.125" customWidth="1"/>
     <col min="33" max="34" width="9.25" customWidth="1"/>
     <col min="35" max="35" width="10.875" customWidth="1"/>
+    <col min="46" max="46" width="7.125" customWidth="1"/>
+    <col min="47" max="47" width="13" customWidth="1"/>
+    <col min="48" max="48" width="11.125" customWidth="1"/>
+    <col min="49" max="49" width="12.875" customWidth="1"/>
+    <col min="50" max="50" width="11.25" customWidth="1"/>
+    <col min="51" max="51" width="14.125" customWidth="1"/>
+    <col min="52" max="52" width="13.125" customWidth="1"/>
+    <col min="53" max="53" width="12.375" customWidth="1"/>
+    <col min="55" max="55" width="10.75" customWidth="1"/>
+    <col min="56" max="56" width="10.625" customWidth="1"/>
+    <col min="57" max="57" width="33.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:46">
+    <row r="1" customFormat="1" spans="1:57">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1432,153 +1512,225 @@
       <c r="AS1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="3" t="s">
+      <c r="AT1" s="1" t="s">
         <v>45</v>
       </c>
+      <c r="AU1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BB1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="BC1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="BD1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="BE1" s="4" t="s">
+        <v>56</v>
+      </c>
     </row>
-    <row r="2" spans="1:46">
+    <row r="2" spans="1:57">
       <c r="A2" s="1" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="AD2" s="1" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="AE2" s="1" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="AF2" s="1" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AG2" s="1" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH2" s="1" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="AJ2" s="1" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="AK2" s="1" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AL2" s="1" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AM2" s="1" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AN2" s="1" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="AO2" s="1" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="AP2" s="1" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="AQ2" s="1" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="AR2" s="1" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="AS2" s="1" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="AT2" s="1" t="s">
-        <v>91</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="AU2" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="AV2" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="AW2" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AX2" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AY2" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="AZ2" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="BA2" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="BB2" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="BC2" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="BD2" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="BE2" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="5" spans="45:45">
+      <c r="AS5" s="3"/>
+    </row>
+    <row r="6" spans="45:45">
+      <c r="AS6" s="3"/>
     </row>
   </sheetData>
-  <dataValidations count="6">
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2 AA2 AB2">
+  <dataValidations count="9">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2 AA2 AB2 AV2 AY2">
       <formula1>32874</formula1>
       <formula2>2958101</formula2>
     </dataValidation>
@@ -1586,9 +1738,13 @@
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2 X2 AS2">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2 X2 AS2 AZ2">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AU2">
+      <formula1>0</formula1>
+      <formula2>99999999999</formula2>
     </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AP2">
       <formula1>0</formula1>
@@ -1598,9 +1754,17 @@
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW2">
+      <formula1>0</formula1>
+      <formula2>999999999</formula2>
+    </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AO2">
       <formula1>0</formula1>
       <formula2>9999999999999</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX2">
+      <formula1>0</formula1>
+      <formula2>999999999</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetail.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetail.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="116">
   <si>
     <t>sku</t>
   </si>
@@ -160,6 +160,9 @@
     <t>首批下单时间</t>
   </si>
   <si>
+    <t>预计首批到货时间</t>
+  </si>
+  <si>
     <t>MOQ(最小起订量)</t>
   </si>
   <si>
@@ -329,6 +332,9 @@
   </si>
   <si>
     <t>{.placeOrderTime}</t>
+  </si>
+  <si>
+    <t>{.planArrivalTime}</t>
   </si>
   <si>
     <t>{.moq}</t>
@@ -1343,7 +1349,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BE6"/>
+  <dimension ref="A1:BF6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
   <cols>
     <col min="14" max="14" width="11.5" customWidth="1"/>
@@ -1366,17 +1372,18 @@
     <col min="46" max="46" width="7.125" customWidth="1"/>
     <col min="47" max="47" width="13" customWidth="1"/>
     <col min="48" max="48" width="11.125" customWidth="1"/>
-    <col min="49" max="49" width="12.875" customWidth="1"/>
+    <col min="49" max="49" width="14.5" customWidth="1"/>
     <col min="50" max="50" width="11.25" customWidth="1"/>
     <col min="51" max="51" width="14.125" customWidth="1"/>
-    <col min="52" max="52" width="13.125" customWidth="1"/>
+    <col min="52" max="52" width="14.875" customWidth="1"/>
     <col min="53" max="53" width="12.375" customWidth="1"/>
     <col min="55" max="55" width="10.75" customWidth="1"/>
     <col min="56" max="56" width="10.625" customWidth="1"/>
-    <col min="57" max="57" width="33.375" customWidth="1"/>
+    <col min="57" max="57" width="11.125" customWidth="1"/>
+    <col min="58" max="58" width="34.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:57">
+    <row r="1" customFormat="1" spans="1:58">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1545,181 +1552,187 @@
       <c r="BD1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" s="4" t="s">
+      <c r="BE1" s="1" t="s">
         <v>56</v>
       </c>
+      <c r="BF1" s="4" t="s">
+        <v>57</v>
+      </c>
     </row>
-    <row r="2" spans="1:57">
+    <row r="2" spans="1:58">
       <c r="A2" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AD2" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AE2" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AF2" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AG2" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AH2" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AJ2" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AK2" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AL2" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AM2" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AN2" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AO2" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AP2" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AQ2" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AR2" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AS2" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AT2" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AU2" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="AW2" s="1" t="s">
         <v>105</v>
       </c>
+      <c r="AW2" s="2" t="s">
+        <v>106</v>
+      </c>
       <c r="AX2" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="AY2" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="AZ2" s="1" t="s">
+      <c r="AY2" s="1" t="s">
         <v>108</v>
       </c>
+      <c r="AZ2" s="2" t="s">
+        <v>109</v>
+      </c>
       <c r="BA2" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BB2" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BC2" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BD2" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BE2" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
+      </c>
+      <c r="BF2" s="1" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="45:45">
@@ -1730,7 +1743,7 @@
     </row>
   </sheetData>
   <dataValidations count="9">
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2 AA2 AB2 AV2 AY2">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2 AA2 AB2 AV2 AW2 AZ2">
       <formula1>32874</formula1>
       <formula2>2958101</formula2>
     </dataValidation>
@@ -1738,7 +1751,7 @@
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2 X2 AS2 AZ2">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2 X2 AS2 BA2">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
@@ -1754,7 +1767,7 @@
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW2">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX2">
       <formula1>0</formula1>
       <formula2>999999999</formula2>
     </dataValidation>
@@ -1762,7 +1775,7 @@
       <formula1>0</formula1>
       <formula2>9999999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX2">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY2">
       <formula1>0</formula1>
       <formula2>999999999</formula2>
     </dataValidation>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetail.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetail.xlsx
@@ -1641,7 +1641,7 @@
       <c r="AA2" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="AB2" s="1" t="s">
+      <c r="AB2" s="2" t="s">
         <v>85</v>
       </c>
       <c r="AC2" s="1" t="s">

--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetail.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetail.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="120">
   <si>
     <t>sku</t>
   </si>
@@ -187,6 +187,12 @@
     <t>二级供应商</t>
   </si>
   <si>
+    <t>量产入库时间</t>
+  </si>
+  <si>
+    <t>产品开发状态</t>
+  </si>
+  <si>
     <t>错误信息</t>
   </si>
   <si>
@@ -359,6 +365,12 @@
   </si>
   <si>
     <t>{.secondSupplier}</t>
+  </si>
+  <si>
+    <t>{.firstMassProductDate}</t>
+  </si>
+  <si>
+    <t>{.productState}</t>
   </si>
   <si>
     <t>{.errorMsg}</t>
@@ -1349,7 +1361,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BF6"/>
+  <dimension ref="A1:BH6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
   <cols>
     <col min="14" max="14" width="11.5" customWidth="1"/>
@@ -1379,11 +1391,11 @@
     <col min="53" max="53" width="12.375" customWidth="1"/>
     <col min="55" max="55" width="10.75" customWidth="1"/>
     <col min="56" max="56" width="10.625" customWidth="1"/>
-    <col min="57" max="57" width="11.125" customWidth="1"/>
-    <col min="58" max="58" width="34.125" customWidth="1"/>
+    <col min="57" max="59" width="11.125" customWidth="1"/>
+    <col min="60" max="60" width="34.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:58">
+    <row r="1" customFormat="1" spans="1:60">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1555,184 +1567,196 @@
       <c r="BE1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" s="4" t="s">
+      <c r="BF1" s="1" t="s">
         <v>57</v>
       </c>
+      <c r="BG1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BH1" s="4" t="s">
+        <v>59</v>
+      </c>
     </row>
-    <row r="2" spans="1:58">
+    <row r="2" spans="1:60">
       <c r="A2" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AD2" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AE2" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AF2" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AG2" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AH2" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AJ2" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AK2" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AL2" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AM2" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AN2" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AO2" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AP2" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AQ2" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AR2" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AS2" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AT2" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AU2" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AX2" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AY2" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="BA2" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="BB2" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="BC2" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="BD2" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="BE2" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="BF2" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
+      </c>
+      <c r="BG2" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="BH2" s="1" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="45:45">

--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetail.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetail.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="128">
   <si>
     <t>sku</t>
   </si>
@@ -133,7 +133,13 @@
     <t>英文用途</t>
   </si>
   <si>
-    <t>产品尺寸</t>
+    <t>产品尺寸(长)</t>
+  </si>
+  <si>
+    <t>产品尺寸(宽)</t>
+  </si>
+  <si>
+    <t>产品尺寸(高)</t>
   </si>
   <si>
     <t>毛重</t>
@@ -142,7 +148,13 @@
     <t>净重</t>
   </si>
   <si>
-    <t>箱规</t>
+    <t>箱规(长)</t>
+  </si>
+  <si>
+    <t>箱规(宽)</t>
+  </si>
+  <si>
+    <t>箱规(高)</t>
   </si>
   <si>
     <t>单箱重量</t>
@@ -313,7 +325,13 @@
     <t>{.englishUsage}</t>
   </si>
   <si>
-    <t>{.productSize}</t>
+    <t>{.productSizeLength}</t>
+  </si>
+  <si>
+    <t>{.productSizeWide}</t>
+  </si>
+  <si>
+    <t>{.productSizeHigh}</t>
   </si>
   <si>
     <t>{.grossWeight}</t>
@@ -322,7 +340,13 @@
     <t>{.netWeight}</t>
   </si>
   <si>
-    <t>{.boxSize}</t>
+    <t>{.boxSizeLength}</t>
+  </si>
+  <si>
+    <t>{.boxSizeWide}</t>
+  </si>
+  <si>
+    <t>{.boxSizeHigh}</t>
   </si>
   <si>
     <t>{.boxWeight}</t>
@@ -370,7 +394,7 @@
     <t>{.firstMassProductDate}</t>
   </si>
   <si>
-    <t>{.productState}</t>
+    <t>{.productStateName}</t>
   </si>
   <si>
     <t>{.errorMsg}</t>
@@ -1361,7 +1385,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BH6"/>
+  <dimension ref="A1:BL6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
   <cols>
     <col min="14" max="14" width="11.5" customWidth="1"/>
@@ -1381,21 +1405,21 @@
     <col min="31" max="32" width="8.125" customWidth="1"/>
     <col min="33" max="34" width="9.25" customWidth="1"/>
     <col min="35" max="35" width="10.875" customWidth="1"/>
-    <col min="46" max="46" width="7.125" customWidth="1"/>
-    <col min="47" max="47" width="13" customWidth="1"/>
-    <col min="48" max="48" width="11.125" customWidth="1"/>
-    <col min="49" max="49" width="14.5" customWidth="1"/>
-    <col min="50" max="50" width="11.25" customWidth="1"/>
-    <col min="51" max="51" width="14.125" customWidth="1"/>
-    <col min="52" max="52" width="14.875" customWidth="1"/>
-    <col min="53" max="53" width="12.375" customWidth="1"/>
-    <col min="55" max="55" width="10.75" customWidth="1"/>
-    <col min="56" max="56" width="10.625" customWidth="1"/>
-    <col min="57" max="59" width="11.125" customWidth="1"/>
-    <col min="60" max="60" width="34.125" customWidth="1"/>
+    <col min="50" max="50" width="7.125" customWidth="1"/>
+    <col min="51" max="51" width="13" customWidth="1"/>
+    <col min="52" max="52" width="11.125" customWidth="1"/>
+    <col min="53" max="53" width="14.5" customWidth="1"/>
+    <col min="54" max="54" width="11.25" customWidth="1"/>
+    <col min="55" max="55" width="14.125" customWidth="1"/>
+    <col min="56" max="56" width="14.875" customWidth="1"/>
+    <col min="57" max="57" width="12.375" customWidth="1"/>
+    <col min="59" max="59" width="10.75" customWidth="1"/>
+    <col min="60" max="60" width="10.625" customWidth="1"/>
+    <col min="61" max="63" width="11.125" customWidth="1"/>
+    <col min="64" max="64" width="34.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:60">
+    <row r="1" customFormat="1" spans="1:64">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1573,201 +1597,225 @@
       <c r="BG1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="BH1" s="4" t="s">
+      <c r="BH1" s="1" t="s">
         <v>59</v>
       </c>
+      <c r="BI1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BJ1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BK1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BL1" s="4" t="s">
+        <v>63</v>
+      </c>
     </row>
-    <row r="2" spans="1:60">
+    <row r="2" spans="1:64">
       <c r="A2" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="AD2" s="1" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="AE2" s="1" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AF2" s="1" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="AG2" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="AH2" s="1" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="AJ2" s="1" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="AK2" s="1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="AL2" s="1" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="AM2" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="AN2" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="AO2" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="AP2" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="AQ2" s="1" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="AR2" s="1" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="AS2" s="1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="AT2" s="1" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="AU2" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="AV2" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="AW2" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
+      </c>
+      <c r="AV2" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="AW2" s="1" t="s">
+        <v>112</v>
       </c>
       <c r="AX2" s="1" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="AY2" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="BA2" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
+      </c>
+      <c r="BA2" s="2" t="s">
+        <v>116</v>
       </c>
       <c r="BB2" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="BC2" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="BD2" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
+      </c>
+      <c r="BD2" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="BE2" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="BF2" s="1" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="BG2" s="1" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="BH2" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
+      </c>
+      <c r="BI2" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="BJ2" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="BK2" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="BL2" s="1" t="s">
+        <v>127</v>
       </c>
     </row>
-    <row r="5" spans="45:45">
-      <c r="AS5" s="3"/>
+    <row r="5" spans="49:49">
+      <c r="AW5" s="3"/>
     </row>
-    <row r="6" spans="45:45">
-      <c r="AS6" s="3"/>
+    <row r="6" spans="49:49">
+      <c r="AW6" s="3"/>
     </row>
   </sheetData>
-  <dataValidations count="9">
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2 AA2 AB2 AV2 AW2 AZ2">
+  <dataValidations count="10">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2 AA2 AB2 AZ2 BA2 BD2">
       <formula1>32874</formula1>
       <formula2>2958101</formula2>
     </dataValidation>
@@ -1775,31 +1823,35 @@
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2 X2 AS2 BA2">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2 X2 AW2 BE2">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AU2">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY2">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AP2">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AR2">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2 Y2 AR2">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2 Y2 AV2">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AX2">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN2:AP2 AS2:AU2">
+      <formula1>0</formula1>
+      <formula2>99999999999999</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AQ2">
+      <formula1>0</formula1>
+      <formula2>9999999999999</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BB2">
       <formula1>0</formula1>
       <formula2>999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AO2">
-      <formula1>0</formula1>
-      <formula2>9999999999999</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY2">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BC2">
       <formula1>0</formula1>
       <formula2>999999999</formula2>
     </dataValidation>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetail.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetail.xlsx
@@ -1815,21 +1815,21 @@
     </row>
   </sheetData>
   <dataValidations count="10">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2 X2">
+      <formula1>0</formula1>
+      <formula2>9999999999</formula2>
+    </dataValidation>
     <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2 AA2 AB2 AZ2 BA2 BD2">
       <formula1>32874</formula1>
       <formula2>2958101</formula2>
     </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN2:AP2 AS2:AU2">
+      <formula1>0</formula1>
+      <formula2>99999999999999</formula2>
+    </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:U2">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2 X2 AW2 BE2">
-      <formula1>0</formula1>
-      <formula2>9999999999</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY2">
-      <formula1>0</formula1>
-      <formula2>99999999999</formula2>
     </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AR2">
       <formula1>0</formula1>
@@ -1839,17 +1839,17 @@
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN2:AP2 AS2:AU2">
-      <formula1>0</formula1>
-      <formula2>99999999999999</formula2>
-    </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AQ2">
       <formula1>0</formula1>
       <formula2>9999999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BB2">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW2">
       <formula1>0</formula1>
-      <formula2>999999999</formula2>
+      <formula2>9999999999</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY2 BB2 BE2">
+      <formula1>0</formula1>
+      <formula2>99999999999</formula2>
     </dataValidation>
     <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BC2">
       <formula1>0</formula1>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetail.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetail.xlsx
@@ -14,11 +14,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="130">
   <si>
     <t>sku</t>
   </si>
   <si>
+    <t>产品分类</t>
+  </si>
+  <si>
     <t>销售方式</t>
   </si>
   <si>
@@ -211,6 +214,9 @@
     <t>{.skuNo}</t>
   </si>
   <si>
+    <t>{.category}</t>
+  </si>
+  <si>
     <t>{.saleMethod}</t>
   </si>
   <si>
@@ -238,7 +244,7 @@
     <t>{.property}</t>
   </si>
   <si>
-    <t>{.planListingTime}</t>
+    <t>{.planListingTimeStr}</t>
   </si>
   <si>
     <t>{.unitName}</t>
@@ -271,25 +277,25 @@
     <t>{.actualGpmUsd}</t>
   </si>
   <si>
-    <t>{.yearSaleQty}</t>
-  </si>
-  <si>
-    <t>{.yearSaleAmount}</t>
-  </si>
-  <si>
-    <t>{.monthSaleQty}</t>
-  </si>
-  <si>
-    <t>{.monthSaleAmount}</t>
+    <t>{.yearSaleQtyStr}</t>
+  </si>
+  <si>
+    <t>{.yearSaleAmountStr}</t>
+  </si>
+  <si>
+    <t>{.monthSaleQtyStr}</t>
+  </si>
+  <si>
+    <t>{.monthSaleAmountStr}</t>
   </si>
   <si>
     <t>{.saleCountry}</t>
   </si>
   <si>
-    <t>{.listingTime}</t>
-  </si>
-  <si>
-    <t>{.delistingTime}</t>
+    <t>{.listingTimeStr}</t>
+  </si>
+  <si>
+    <t>{.delistingTimeStr}</t>
   </si>
   <si>
     <t>{.isFinishedImg}</t>
@@ -310,7 +316,7 @@
     <t>{.declareEnglishName}</t>
   </si>
   <si>
-    <t>{.declarePrice}</t>
+    <t>{.declarePriceStr}</t>
   </si>
   <si>
     <t>{.customsCode}</t>
@@ -325,58 +331,58 @@
     <t>{.englishUsage}</t>
   </si>
   <si>
-    <t>{.productSizeLength}</t>
-  </si>
-  <si>
-    <t>{.productSizeWide}</t>
-  </si>
-  <si>
-    <t>{.productSizeHigh}</t>
-  </si>
-  <si>
-    <t>{.grossWeight}</t>
-  </si>
-  <si>
-    <t>{.netWeight}</t>
-  </si>
-  <si>
-    <t>{.boxSizeLength}</t>
-  </si>
-  <si>
-    <t>{.boxSizeWide}</t>
-  </si>
-  <si>
-    <t>{.boxSizeHigh}</t>
-  </si>
-  <si>
-    <t>{.boxWeight}</t>
-  </si>
-  <si>
-    <t>{.boxQty}</t>
+    <t>{.productSizeLengthStr}</t>
+  </si>
+  <si>
+    <t>{.productSizeWideStr}</t>
+  </si>
+  <si>
+    <t>{.productSizeHighStr}</t>
+  </si>
+  <si>
+    <t>{.grossWeightStr}</t>
+  </si>
+  <si>
+    <t>{.netWeightStr}</t>
+  </si>
+  <si>
+    <t>{.boxSizeLengthStr}</t>
+  </si>
+  <si>
+    <t>{.boxSizeWideStr}</t>
+  </si>
+  <si>
+    <t>{.boxSizeHighStr}</t>
+  </si>
+  <si>
+    <t>{.boxWeightStr}</t>
+  </si>
+  <si>
+    <t>{.boxQtyStr}</t>
   </si>
   <si>
     <t>{.ean}</t>
   </si>
   <si>
-    <t>{.planOrderQty}</t>
-  </si>
-  <si>
-    <t>{.placeOrderTime}</t>
-  </si>
-  <si>
-    <t>{.planArrivalTime}</t>
-  </si>
-  <si>
-    <t>{.moq}</t>
-  </si>
-  <si>
-    <t>{.deliveryCycle}</t>
-  </si>
-  <si>
-    <t>{.actualArrivalTime}</t>
-  </si>
-  <si>
-    <t>{.actualArrivalQty}</t>
+    <t>{.planOrderQtyStr}</t>
+  </si>
+  <si>
+    <t>{.placeOrderTimeStr}</t>
+  </si>
+  <si>
+    <t>{.planArrivalTimeStr}</t>
+  </si>
+  <si>
+    <t>{.moqStr}</t>
+  </si>
+  <si>
+    <t>{.deliveryCycleStr}</t>
+  </si>
+  <si>
+    <t>{.actualArrivalTimeStr}</t>
+  </si>
+  <si>
+    <t>{.actualArrivalQtyStr}</t>
   </si>
   <si>
     <t>{.arrivalState}</t>
@@ -391,7 +397,7 @@
     <t>{.secondSupplier}</t>
   </si>
   <si>
-    <t>{.firstMassProductDate}</t>
+    <t>{.firstMassProductDateStr}</t>
   </si>
   <si>
     <t>{.productStateName}</t>
@@ -1385,41 +1391,41 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BL6"/>
+  <dimension ref="A1:BM6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
   <cols>
-    <col min="14" max="14" width="11.5" customWidth="1"/>
-    <col min="15" max="15" width="13" customWidth="1"/>
-    <col min="16" max="16" width="11" customWidth="1"/>
-    <col min="17" max="17" width="13.25" customWidth="1"/>
-    <col min="18" max="18" width="9.625" customWidth="1"/>
-    <col min="19" max="19" width="9.375" customWidth="1"/>
-    <col min="20" max="20" width="16" customWidth="1"/>
-    <col min="21" max="21" width="14.875" customWidth="1"/>
-    <col min="22" max="22" width="12" customWidth="1"/>
-    <col min="23" max="23" width="12.375" customWidth="1"/>
-    <col min="24" max="24" width="12.125" customWidth="1"/>
-    <col min="25" max="25" width="12.25" customWidth="1"/>
-    <col min="29" max="29" width="12.25" customWidth="1"/>
-    <col min="30" max="30" width="11.125" customWidth="1"/>
-    <col min="31" max="32" width="8.125" customWidth="1"/>
-    <col min="33" max="34" width="9.25" customWidth="1"/>
-    <col min="35" max="35" width="10.875" customWidth="1"/>
-    <col min="50" max="50" width="7.125" customWidth="1"/>
-    <col min="51" max="51" width="13" customWidth="1"/>
-    <col min="52" max="52" width="11.125" customWidth="1"/>
-    <col min="53" max="53" width="14.5" customWidth="1"/>
-    <col min="54" max="54" width="11.25" customWidth="1"/>
-    <col min="55" max="55" width="14.125" customWidth="1"/>
-    <col min="56" max="56" width="14.875" customWidth="1"/>
-    <col min="57" max="57" width="12.375" customWidth="1"/>
-    <col min="59" max="59" width="10.75" customWidth="1"/>
-    <col min="60" max="60" width="10.625" customWidth="1"/>
-    <col min="61" max="63" width="11.125" customWidth="1"/>
-    <col min="64" max="64" width="34.125" customWidth="1"/>
+    <col min="15" max="15" width="11.5" customWidth="1"/>
+    <col min="16" max="16" width="13" customWidth="1"/>
+    <col min="17" max="17" width="11" customWidth="1"/>
+    <col min="18" max="18" width="13.25" customWidth="1"/>
+    <col min="19" max="19" width="9.625" customWidth="1"/>
+    <col min="20" max="20" width="9.375" customWidth="1"/>
+    <col min="21" max="21" width="16" customWidth="1"/>
+    <col min="22" max="22" width="14.875" customWidth="1"/>
+    <col min="23" max="23" width="12" customWidth="1"/>
+    <col min="24" max="24" width="12.375" customWidth="1"/>
+    <col min="25" max="25" width="12.125" customWidth="1"/>
+    <col min="26" max="26" width="12.25" customWidth="1"/>
+    <col min="30" max="30" width="12.25" customWidth="1"/>
+    <col min="31" max="31" width="11.125" customWidth="1"/>
+    <col min="32" max="33" width="8.125" customWidth="1"/>
+    <col min="34" max="35" width="9.25" customWidth="1"/>
+    <col min="36" max="36" width="10.875" customWidth="1"/>
+    <col min="51" max="51" width="7.125" customWidth="1"/>
+    <col min="52" max="52" width="13" customWidth="1"/>
+    <col min="53" max="53" width="11.125" customWidth="1"/>
+    <col min="54" max="54" width="14.5" customWidth="1"/>
+    <col min="55" max="55" width="11.25" customWidth="1"/>
+    <col min="56" max="56" width="14.125" customWidth="1"/>
+    <col min="57" max="57" width="14.875" customWidth="1"/>
+    <col min="58" max="58" width="12.375" customWidth="1"/>
+    <col min="60" max="60" width="10.75" customWidth="1"/>
+    <col min="61" max="61" width="10.625" customWidth="1"/>
+    <col min="62" max="64" width="11.125" customWidth="1"/>
+    <col min="65" max="65" width="34.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:64">
+    <row r="1" customFormat="1" spans="1:65">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1609,253 +1615,217 @@
       <c r="BK1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="BL1" s="4" t="s">
+      <c r="BL1" s="1" t="s">
         <v>63</v>
       </c>
+      <c r="BM1" s="4" t="s">
+        <v>64</v>
+      </c>
     </row>
-    <row r="2" spans="1:64">
+    <row r="2" spans="1:65">
       <c r="A2" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="K2" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>75</v>
       </c>
+      <c r="L2" s="2" t="s">
+        <v>76</v>
+      </c>
       <c r="M2" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="AA2" s="2" t="s">
         <v>90</v>
       </c>
+      <c r="AA2" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="AB2" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="AC2" s="1" t="s">
         <v>92</v>
       </c>
+      <c r="AC2" s="2" t="s">
+        <v>93</v>
+      </c>
       <c r="AD2" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AE2" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AF2" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AG2" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AH2" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AJ2" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK2" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AL2" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AM2" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AN2" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO2" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AP2" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AQ2" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AR2" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AS2" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AT2" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AU2" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AV2" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AW2" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AX2" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AY2" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="AZ2" s="2" t="s">
         <v>115</v>
       </c>
+      <c r="AZ2" s="1" t="s">
+        <v>116</v>
+      </c>
       <c r="BA2" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="BB2" s="1" t="s">
         <v>117</v>
       </c>
+      <c r="BB2" s="2" t="s">
+        <v>118</v>
+      </c>
       <c r="BC2" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="BD2" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="BE2" s="1" t="s">
+      <c r="BD2" s="1" t="s">
         <v>120</v>
       </c>
+      <c r="BE2" s="2" t="s">
+        <v>121</v>
+      </c>
       <c r="BF2" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="BG2" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BH2" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="BI2" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="BJ2" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="BK2" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BL2" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
+      </c>
+      <c r="BM2" s="1" t="s">
+        <v>129</v>
       </c>
     </row>
-    <row r="5" spans="49:49">
-      <c r="AW5" s="3"/>
+    <row r="5" spans="50:50">
+      <c r="AX5" s="3"/>
     </row>
-    <row r="6" spans="49:49">
-      <c r="AW6" s="3"/>
+    <row r="6" spans="50:50">
+      <c r="AX6" s="3"/>
     </row>
   </sheetData>
-  <dataValidations count="10">
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2 X2">
-      <formula1>0</formula1>
-      <formula2>9999999999</formula2>
-    </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2 AA2 AB2 AZ2 BA2 BD2">
-      <formula1>32874</formula1>
-      <formula2>2958101</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN2:AP2 AS2:AU2">
-      <formula1>0</formula1>
-      <formula2>99999999999999</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:U2">
-      <formula1>0</formula1>
-      <formula2>999999999999</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AR2">
-      <formula1>0</formula1>
-      <formula2>99999999999</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2 Y2 AV2">
-      <formula1>0</formula1>
-      <formula2>9999999999</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AQ2">
-      <formula1>0</formula1>
-      <formula2>9999999999999</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AW2">
-      <formula1>0</formula1>
-      <formula2>9999999999</formula2>
-    </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY2 BB2 BE2">
-      <formula1>0</formula1>
-      <formula2>99999999999</formula2>
-    </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BC2">
-      <formula1>0</formula1>
-      <formula2>999999999</formula2>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetail.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetail.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12540"/>
+    <workbookView windowWidth="28125" windowHeight="11940"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -220,10 +220,10 @@
     <t>{.saleMethod}</t>
   </si>
   <si>
-    <t>{.productSellSpot}</t>
-  </si>
-  <si>
-    <t>{.productFunctionDesc}</t>
+    <t>{.sellSpot}</t>
+  </si>
+  <si>
+    <t>{.functionDesc}</t>
   </si>
   <si>
     <t>{.usageDesc}</t>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetail.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetail.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="132">
   <si>
     <t>sku</t>
   </si>
@@ -43,6 +43,9 @@
     <t>品名</t>
   </si>
   <si>
+    <t>品名（英文）</t>
+  </si>
+  <si>
     <t>品牌</t>
   </si>
   <si>
@@ -236,6 +239,9 @@
   </si>
   <si>
     <t>{.name}</t>
+  </si>
+  <si>
+    <t>{.nameEn}</t>
   </si>
   <si>
     <t>{.brandName}</t>
@@ -1391,41 +1397,41 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BM6"/>
+  <dimension ref="A1:BN6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
   <cols>
-    <col min="15" max="15" width="11.5" customWidth="1"/>
-    <col min="16" max="16" width="13" customWidth="1"/>
-    <col min="17" max="17" width="11" customWidth="1"/>
-    <col min="18" max="18" width="13.25" customWidth="1"/>
-    <col min="19" max="19" width="9.625" customWidth="1"/>
-    <col min="20" max="20" width="9.375" customWidth="1"/>
-    <col min="21" max="21" width="16" customWidth="1"/>
-    <col min="22" max="22" width="14.875" customWidth="1"/>
-    <col min="23" max="23" width="12" customWidth="1"/>
-    <col min="24" max="24" width="12.375" customWidth="1"/>
-    <col min="25" max="25" width="12.125" customWidth="1"/>
-    <col min="26" max="26" width="12.25" customWidth="1"/>
-    <col min="30" max="30" width="12.25" customWidth="1"/>
-    <col min="31" max="31" width="11.125" customWidth="1"/>
-    <col min="32" max="33" width="8.125" customWidth="1"/>
-    <col min="34" max="35" width="9.25" customWidth="1"/>
-    <col min="36" max="36" width="10.875" customWidth="1"/>
-    <col min="51" max="51" width="7.125" customWidth="1"/>
-    <col min="52" max="52" width="13" customWidth="1"/>
-    <col min="53" max="53" width="11.125" customWidth="1"/>
-    <col min="54" max="54" width="14.5" customWidth="1"/>
-    <col min="55" max="55" width="11.25" customWidth="1"/>
-    <col min="56" max="56" width="14.125" customWidth="1"/>
-    <col min="57" max="57" width="14.875" customWidth="1"/>
-    <col min="58" max="58" width="12.375" customWidth="1"/>
-    <col min="60" max="60" width="10.75" customWidth="1"/>
-    <col min="61" max="61" width="10.625" customWidth="1"/>
-    <col min="62" max="64" width="11.125" customWidth="1"/>
-    <col min="65" max="65" width="34.125" customWidth="1"/>
+    <col min="16" max="16" width="11.5" customWidth="1"/>
+    <col min="17" max="17" width="13" customWidth="1"/>
+    <col min="18" max="18" width="11" customWidth="1"/>
+    <col min="19" max="19" width="13.25" customWidth="1"/>
+    <col min="20" max="20" width="9.625" customWidth="1"/>
+    <col min="21" max="21" width="9.375" customWidth="1"/>
+    <col min="22" max="22" width="16" customWidth="1"/>
+    <col min="23" max="23" width="14.875" customWidth="1"/>
+    <col min="24" max="24" width="12" customWidth="1"/>
+    <col min="25" max="25" width="12.375" customWidth="1"/>
+    <col min="26" max="26" width="12.125" customWidth="1"/>
+    <col min="27" max="27" width="12.25" customWidth="1"/>
+    <col min="31" max="31" width="12.25" customWidth="1"/>
+    <col min="32" max="32" width="11.125" customWidth="1"/>
+    <col min="33" max="34" width="8.125" customWidth="1"/>
+    <col min="35" max="36" width="9.25" customWidth="1"/>
+    <col min="37" max="37" width="10.875" customWidth="1"/>
+    <col min="52" max="52" width="7.125" customWidth="1"/>
+    <col min="53" max="53" width="13" customWidth="1"/>
+    <col min="54" max="54" width="11.125" customWidth="1"/>
+    <col min="55" max="55" width="14.5" customWidth="1"/>
+    <col min="56" max="56" width="11.25" customWidth="1"/>
+    <col min="57" max="57" width="14.125" customWidth="1"/>
+    <col min="58" max="58" width="14.875" customWidth="1"/>
+    <col min="59" max="59" width="12.375" customWidth="1"/>
+    <col min="61" max="61" width="10.75" customWidth="1"/>
+    <col min="62" max="62" width="10.625" customWidth="1"/>
+    <col min="63" max="65" width="11.125" customWidth="1"/>
+    <col min="66" max="66" width="34.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:65">
+    <row r="1" customFormat="1" spans="1:66">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1618,212 +1624,218 @@
       <c r="BL1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="BM1" s="4" t="s">
+      <c r="BM1" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="BN1" s="4" t="s">
+        <v>65</v>
+      </c>
     </row>
-    <row r="2" spans="1:65">
+    <row r="2" spans="1:66">
       <c r="A2" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="L2" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>77</v>
       </c>
+      <c r="M2" s="2" t="s">
+        <v>78</v>
+      </c>
       <c r="N2" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="AB2" s="2" t="s">
         <v>92</v>
       </c>
+      <c r="AB2" s="1" t="s">
+        <v>93</v>
+      </c>
       <c r="AC2" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="AD2" s="1" t="s">
         <v>94</v>
       </c>
+      <c r="AD2" s="2" t="s">
+        <v>95</v>
+      </c>
       <c r="AE2" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AF2" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG2" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AH2" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AJ2" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AK2" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AL2" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AM2" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AN2" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AO2" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AP2" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AQ2" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AR2" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AS2" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AT2" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AU2" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AV2" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AW2" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AX2" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AY2" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AZ2" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="BA2" s="2" t="s">
         <v>117</v>
       </c>
+      <c r="BA2" s="1" t="s">
+        <v>118</v>
+      </c>
       <c r="BB2" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="BC2" s="1" t="s">
         <v>119</v>
       </c>
+      <c r="BC2" s="2" t="s">
+        <v>120</v>
+      </c>
       <c r="BD2" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="BE2" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="BF2" s="1" t="s">
+      <c r="BE2" s="1" t="s">
         <v>122</v>
       </c>
+      <c r="BF2" s="2" t="s">
+        <v>123</v>
+      </c>
       <c r="BG2" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="BH2" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="BI2" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="BJ2" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BK2" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BL2" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BM2" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
+      </c>
+      <c r="BN2" s="1" t="s">
+        <v>131</v>
       </c>
     </row>
-    <row r="5" spans="50:50">
-      <c r="AX5" s="3"/>
+    <row r="5" spans="51:51">
+      <c r="AY5" s="3"/>
     </row>
-    <row r="6" spans="50:50">
-      <c r="AX6" s="3"/>
+    <row r="6" spans="51:51">
+      <c r="AY6" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetail.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetail.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="11940"/>
+    <workbookView windowWidth="28125" windowHeight="12540"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -14,12 +14,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="136">
+  <si>
+    <t>spu</t>
+  </si>
   <si>
     <t>sku</t>
   </si>
   <si>
-    <t>产品分类</t>
+    <t>一级类目</t>
+  </si>
+  <si>
+    <t>二级类目</t>
   </si>
   <si>
     <t>销售方式</t>
@@ -214,10 +220,16 @@
     <t>错误信息</t>
   </si>
   <si>
+    <t>{.spuNo}</t>
+  </si>
+  <si>
     <t>{.skuNo}</t>
   </si>
   <si>
-    <t>{.category}</t>
+    <t>{.mainCategory}</t>
+  </si>
+  <si>
+    <t>{.secondaryCategory}</t>
   </si>
   <si>
     <t>{.saleMethod}</t>
@@ -1397,41 +1409,41 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BN6"/>
+  <dimension ref="A1:BP6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
   <cols>
-    <col min="16" max="16" width="11.5" customWidth="1"/>
-    <col min="17" max="17" width="13" customWidth="1"/>
-    <col min="18" max="18" width="11" customWidth="1"/>
-    <col min="19" max="19" width="13.25" customWidth="1"/>
-    <col min="20" max="20" width="9.625" customWidth="1"/>
-    <col min="21" max="21" width="9.375" customWidth="1"/>
-    <col min="22" max="22" width="16" customWidth="1"/>
-    <col min="23" max="23" width="14.875" customWidth="1"/>
-    <col min="24" max="24" width="12" customWidth="1"/>
-    <col min="25" max="25" width="12.375" customWidth="1"/>
-    <col min="26" max="26" width="12.125" customWidth="1"/>
-    <col min="27" max="27" width="12.25" customWidth="1"/>
-    <col min="31" max="31" width="12.25" customWidth="1"/>
-    <col min="32" max="32" width="11.125" customWidth="1"/>
-    <col min="33" max="34" width="8.125" customWidth="1"/>
-    <col min="35" max="36" width="9.25" customWidth="1"/>
-    <col min="37" max="37" width="10.875" customWidth="1"/>
-    <col min="52" max="52" width="7.125" customWidth="1"/>
-    <col min="53" max="53" width="13" customWidth="1"/>
-    <col min="54" max="54" width="11.125" customWidth="1"/>
-    <col min="55" max="55" width="14.5" customWidth="1"/>
-    <col min="56" max="56" width="11.25" customWidth="1"/>
-    <col min="57" max="57" width="14.125" customWidth="1"/>
-    <col min="58" max="58" width="14.875" customWidth="1"/>
-    <col min="59" max="59" width="12.375" customWidth="1"/>
-    <col min="61" max="61" width="10.75" customWidth="1"/>
-    <col min="62" max="62" width="10.625" customWidth="1"/>
-    <col min="63" max="65" width="11.125" customWidth="1"/>
-    <col min="66" max="66" width="34.125" customWidth="1"/>
+    <col min="18" max="18" width="11.5" customWidth="1"/>
+    <col min="19" max="19" width="13" customWidth="1"/>
+    <col min="20" max="20" width="11" customWidth="1"/>
+    <col min="21" max="21" width="13.25" customWidth="1"/>
+    <col min="22" max="22" width="9.625" customWidth="1"/>
+    <col min="23" max="23" width="9.375" customWidth="1"/>
+    <col min="24" max="24" width="16" customWidth="1"/>
+    <col min="25" max="25" width="14.875" customWidth="1"/>
+    <col min="26" max="26" width="12" customWidth="1"/>
+    <col min="27" max="27" width="12.375" customWidth="1"/>
+    <col min="28" max="28" width="12.125" customWidth="1"/>
+    <col min="29" max="29" width="12.25" customWidth="1"/>
+    <col min="33" max="33" width="12.25" customWidth="1"/>
+    <col min="34" max="34" width="11.125" customWidth="1"/>
+    <col min="35" max="36" width="8.125" customWidth="1"/>
+    <col min="37" max="38" width="9.25" customWidth="1"/>
+    <col min="39" max="39" width="10.875" customWidth="1"/>
+    <col min="54" max="54" width="7.125" customWidth="1"/>
+    <col min="55" max="55" width="13" customWidth="1"/>
+    <col min="56" max="56" width="11.125" customWidth="1"/>
+    <col min="57" max="57" width="14.5" customWidth="1"/>
+    <col min="58" max="58" width="11.25" customWidth="1"/>
+    <col min="59" max="59" width="14.125" customWidth="1"/>
+    <col min="60" max="60" width="14.875" customWidth="1"/>
+    <col min="61" max="61" width="12.375" customWidth="1"/>
+    <col min="63" max="63" width="10.75" customWidth="1"/>
+    <col min="64" max="64" width="10.625" customWidth="1"/>
+    <col min="65" max="67" width="11.125" customWidth="1"/>
+    <col min="68" max="68" width="34.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:66">
+    <row r="1" customFormat="1" spans="1:68">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1627,215 +1639,227 @@
       <c r="BM1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="BN1" s="4" t="s">
+      <c r="BN1" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="BO1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="BP1" s="4" t="s">
+        <v>67</v>
+      </c>
     </row>
-    <row r="2" spans="1:66">
+    <row r="2" spans="1:68">
       <c r="A2" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>80</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>82</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="AC2" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="AD2" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="AE2" s="1" t="s">
+      <c r="AC2" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="AF2" s="1" t="s">
+      <c r="AD2" s="1" t="s">
         <v>97</v>
       </c>
+      <c r="AE2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AF2" s="2" t="s">
+        <v>99</v>
+      </c>
       <c r="AG2" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AH2" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AJ2" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK2" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AL2" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AM2" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AN2" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AO2" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AP2" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AQ2" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AR2" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AS2" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AT2" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AU2" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AV2" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AW2" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AX2" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AY2" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AZ2" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="BA2" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="BB2" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="BC2" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="BD2" s="1" t="s">
+      <c r="BB2" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="BE2" s="1" t="s">
+      <c r="BC2" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="BF2" s="2" t="s">
+      <c r="BD2" s="2" t="s">
         <v>123</v>
       </c>
+      <c r="BE2" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="BF2" s="1" t="s">
+        <v>125</v>
+      </c>
       <c r="BG2" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="BH2" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
+      </c>
+      <c r="BH2" s="2" t="s">
+        <v>127</v>
       </c>
       <c r="BI2" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="BJ2" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BK2" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="BL2" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="BM2" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="BN2" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
+      </c>
+      <c r="BO2" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="BP2" s="1" t="s">
+        <v>135</v>
       </c>
     </row>
-    <row r="5" spans="51:51">
-      <c r="AY5" s="3"/>
+    <row r="5" spans="53:53">
+      <c r="BA5" s="3"/>
     </row>
-    <row r="6" spans="51:51">
-      <c r="AY6" s="3"/>
+    <row r="6" spans="53:53">
+      <c r="BA6" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetail.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetail.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12540"/>
+    <workbookView windowWidth="28125" windowHeight="11940"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -14,18 +14,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="136">
-  <si>
-    <t>spu</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="132">
   <si>
     <t>sku</t>
   </si>
   <si>
-    <t>一级类目</t>
-  </si>
-  <si>
-    <t>二级类目</t>
+    <t>产品分类</t>
   </si>
   <si>
     <t>销售方式</t>
@@ -220,16 +214,10 @@
     <t>错误信息</t>
   </si>
   <si>
-    <t>{.spuNo}</t>
-  </si>
-  <si>
     <t>{.skuNo}</t>
   </si>
   <si>
-    <t>{.mainCategory}</t>
-  </si>
-  <si>
-    <t>{.secondaryCategory}</t>
+    <t>{.category}</t>
   </si>
   <si>
     <t>{.saleMethod}</t>
@@ -1409,41 +1397,41 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BP6"/>
+  <dimension ref="A1:BN6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
   <cols>
-    <col min="18" max="18" width="11.5" customWidth="1"/>
-    <col min="19" max="19" width="13" customWidth="1"/>
-    <col min="20" max="20" width="11" customWidth="1"/>
-    <col min="21" max="21" width="13.25" customWidth="1"/>
-    <col min="22" max="22" width="9.625" customWidth="1"/>
-    <col min="23" max="23" width="9.375" customWidth="1"/>
-    <col min="24" max="24" width="16" customWidth="1"/>
-    <col min="25" max="25" width="14.875" customWidth="1"/>
-    <col min="26" max="26" width="12" customWidth="1"/>
-    <col min="27" max="27" width="12.375" customWidth="1"/>
-    <col min="28" max="28" width="12.125" customWidth="1"/>
-    <col min="29" max="29" width="12.25" customWidth="1"/>
-    <col min="33" max="33" width="12.25" customWidth="1"/>
-    <col min="34" max="34" width="11.125" customWidth="1"/>
-    <col min="35" max="36" width="8.125" customWidth="1"/>
-    <col min="37" max="38" width="9.25" customWidth="1"/>
-    <col min="39" max="39" width="10.875" customWidth="1"/>
-    <col min="54" max="54" width="7.125" customWidth="1"/>
-    <col min="55" max="55" width="13" customWidth="1"/>
-    <col min="56" max="56" width="11.125" customWidth="1"/>
-    <col min="57" max="57" width="14.5" customWidth="1"/>
-    <col min="58" max="58" width="11.25" customWidth="1"/>
-    <col min="59" max="59" width="14.125" customWidth="1"/>
-    <col min="60" max="60" width="14.875" customWidth="1"/>
-    <col min="61" max="61" width="12.375" customWidth="1"/>
-    <col min="63" max="63" width="10.75" customWidth="1"/>
-    <col min="64" max="64" width="10.625" customWidth="1"/>
-    <col min="65" max="67" width="11.125" customWidth="1"/>
-    <col min="68" max="68" width="34.125" customWidth="1"/>
+    <col min="16" max="16" width="11.5" customWidth="1"/>
+    <col min="17" max="17" width="13" customWidth="1"/>
+    <col min="18" max="18" width="11" customWidth="1"/>
+    <col min="19" max="19" width="13.25" customWidth="1"/>
+    <col min="20" max="20" width="9.625" customWidth="1"/>
+    <col min="21" max="21" width="9.375" customWidth="1"/>
+    <col min="22" max="22" width="16" customWidth="1"/>
+    <col min="23" max="23" width="14.875" customWidth="1"/>
+    <col min="24" max="24" width="12" customWidth="1"/>
+    <col min="25" max="25" width="12.375" customWidth="1"/>
+    <col min="26" max="26" width="12.125" customWidth="1"/>
+    <col min="27" max="27" width="12.25" customWidth="1"/>
+    <col min="31" max="31" width="12.25" customWidth="1"/>
+    <col min="32" max="32" width="11.125" customWidth="1"/>
+    <col min="33" max="34" width="8.125" customWidth="1"/>
+    <col min="35" max="36" width="9.25" customWidth="1"/>
+    <col min="37" max="37" width="10.875" customWidth="1"/>
+    <col min="52" max="52" width="7.125" customWidth="1"/>
+    <col min="53" max="53" width="13" customWidth="1"/>
+    <col min="54" max="54" width="11.125" customWidth="1"/>
+    <col min="55" max="55" width="14.5" customWidth="1"/>
+    <col min="56" max="56" width="11.25" customWidth="1"/>
+    <col min="57" max="57" width="14.125" customWidth="1"/>
+    <col min="58" max="58" width="14.875" customWidth="1"/>
+    <col min="59" max="59" width="12.375" customWidth="1"/>
+    <col min="61" max="61" width="10.75" customWidth="1"/>
+    <col min="62" max="62" width="10.625" customWidth="1"/>
+    <col min="63" max="65" width="11.125" customWidth="1"/>
+    <col min="66" max="66" width="34.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:68">
+    <row r="1" customFormat="1" spans="1:66">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1639,227 +1627,215 @@
       <c r="BM1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="BN1" s="1" t="s">
+      <c r="BN1" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="BO1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:66">
+      <c r="A2" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="BP1" s="4" t="s">
+      <c r="B2" s="1" t="s">
         <v>67</v>
       </c>
+      <c r="C2" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC2" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="AD2" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AE2" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="AF2" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="AG2" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="AH2" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="AI2" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="AJ2" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="AK2" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="AL2" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="AM2" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="AN2" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AO2" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AP2" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="AQ2" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="AR2" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="AS2" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="AT2" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="AU2" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="AV2" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AW2" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="AX2" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="AY2" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="AZ2" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="BA2" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="BB2" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BC2" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="BD2" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="BE2" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="BF2" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="BG2" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="BH2" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="BI2" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="BJ2" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="BK2" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="BL2" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="BM2" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="BN2" s="1" t="s">
+        <v>131</v>
+      </c>
     </row>
-    <row r="2" spans="1:68">
-      <c r="A2" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="AC2" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="AD2" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="AE2" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="AF2" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="AG2" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="AH2" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="AI2" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="AJ2" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="AK2" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="AL2" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="AM2" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="AN2" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="AO2" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="AP2" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="AQ2" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="AR2" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="AS2" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="AT2" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="AU2" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="AV2" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AW2" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX2" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="AY2" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="AZ2" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="BA2" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="BB2" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="BC2" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="BD2" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BE2" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="BF2" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="BG2" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="BH2" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="BI2" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="BJ2" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="BK2" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="BL2" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="BM2" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="BN2" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="BO2" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="BP2" s="1" t="s">
-        <v>135</v>
-      </c>
+    <row r="5" spans="51:51">
+      <c r="AY5" s="3"/>
     </row>
-    <row r="5" spans="53:53">
-      <c r="BA5" s="3"/>
-    </row>
-    <row r="6" spans="53:53">
-      <c r="BA6" s="3"/>
+    <row r="6" spans="51:51">
+      <c r="AY6" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetail.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetail.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="11940"/>
+    <workbookView windowWidth="28125" windowHeight="12540"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -14,12 +14,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="136">
+  <si>
+    <t>spu</t>
+  </si>
   <si>
     <t>sku</t>
   </si>
   <si>
-    <t>产品分类</t>
+    <t>一级类目</t>
+  </si>
+  <si>
+    <t>二级类目</t>
   </si>
   <si>
     <t>销售方式</t>
@@ -214,10 +220,16 @@
     <t>错误信息</t>
   </si>
   <si>
+    <t>{.spuNo}</t>
+  </si>
+  <si>
     <t>{.skuNo}</t>
   </si>
   <si>
-    <t>{.category}</t>
+    <t>{.mainCategory}</t>
+  </si>
+  <si>
+    <t>{.secondaryCategory}</t>
   </si>
   <si>
     <t>{.saleMethod}</t>
@@ -1397,42 +1409,42 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BN6"/>
+  <dimension ref="A1:BP6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
   <cols>
-    <col min="16" max="16" width="11.5" customWidth="1"/>
-    <col min="17" max="17" width="13" customWidth="1"/>
-    <col min="18" max="18" width="11" customWidth="1"/>
-    <col min="19" max="19" width="13.25" customWidth="1"/>
-    <col min="20" max="20" width="9.625" customWidth="1"/>
-    <col min="21" max="21" width="9.375" customWidth="1"/>
-    <col min="22" max="22" width="16" customWidth="1"/>
-    <col min="23" max="23" width="14.875" customWidth="1"/>
-    <col min="24" max="24" width="12" customWidth="1"/>
-    <col min="25" max="25" width="12.375" customWidth="1"/>
-    <col min="26" max="26" width="12.125" customWidth="1"/>
-    <col min="27" max="27" width="12.25" customWidth="1"/>
-    <col min="31" max="31" width="12.25" customWidth="1"/>
-    <col min="32" max="32" width="11.125" customWidth="1"/>
-    <col min="33" max="34" width="8.125" customWidth="1"/>
-    <col min="35" max="36" width="9.25" customWidth="1"/>
-    <col min="37" max="37" width="10.875" customWidth="1"/>
-    <col min="52" max="52" width="7.125" customWidth="1"/>
-    <col min="53" max="53" width="13" customWidth="1"/>
-    <col min="54" max="54" width="11.125" customWidth="1"/>
-    <col min="55" max="55" width="14.5" customWidth="1"/>
-    <col min="56" max="56" width="11.25" customWidth="1"/>
-    <col min="57" max="57" width="14.125" customWidth="1"/>
-    <col min="58" max="58" width="14.875" customWidth="1"/>
-    <col min="59" max="59" width="12.375" customWidth="1"/>
-    <col min="61" max="61" width="10.75" customWidth="1"/>
-    <col min="62" max="62" width="10.625" customWidth="1"/>
-    <col min="63" max="65" width="11.125" customWidth="1"/>
-    <col min="66" max="66" width="34.125" customWidth="1"/>
+    <col min="18" max="18" width="11.5" customWidth="1"/>
+    <col min="19" max="19" width="13" customWidth="1"/>
+    <col min="20" max="20" width="11" customWidth="1"/>
+    <col min="21" max="21" width="13.25" customWidth="1"/>
+    <col min="22" max="22" width="9.625" customWidth="1"/>
+    <col min="23" max="23" width="9.375" customWidth="1"/>
+    <col min="24" max="24" width="16" customWidth="1"/>
+    <col min="25" max="25" width="14.875" customWidth="1"/>
+    <col min="26" max="26" width="12" customWidth="1"/>
+    <col min="27" max="27" width="12.375" customWidth="1"/>
+    <col min="28" max="28" width="12.125" customWidth="1"/>
+    <col min="29" max="29" width="12.25" customWidth="1"/>
+    <col min="33" max="33" width="12.25" customWidth="1"/>
+    <col min="34" max="34" width="11.125" customWidth="1"/>
+    <col min="35" max="36" width="8.125" customWidth="1"/>
+    <col min="37" max="38" width="9.25" customWidth="1"/>
+    <col min="39" max="39" width="10.875" customWidth="1"/>
+    <col min="54" max="54" width="7.125" customWidth="1"/>
+    <col min="55" max="55" width="13" customWidth="1"/>
+    <col min="56" max="56" width="11.125" customWidth="1"/>
+    <col min="57" max="57" width="14.5" customWidth="1"/>
+    <col min="58" max="58" width="11.25" customWidth="1"/>
+    <col min="59" max="59" width="14.125" customWidth="1"/>
+    <col min="60" max="60" width="14.875" customWidth="1"/>
+    <col min="61" max="61" width="12.375" customWidth="1"/>
+    <col min="63" max="63" width="10.75" customWidth="1"/>
+    <col min="64" max="64" width="10.625" customWidth="1"/>
+    <col min="65" max="67" width="11.125" customWidth="1"/>
+    <col min="68" max="68" width="34.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:66">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="1" spans="1:68">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -1627,215 +1639,227 @@
       <c r="BM1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="BN1" s="4" t="s">
+      <c r="BN1" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="BO1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="BP1" s="4" t="s">
+        <v>67</v>
+      </c>
     </row>
-    <row r="2" spans="1:66">
+    <row r="2" spans="1:68">
       <c r="A2" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>80</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>82</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="AC2" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="AD2" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="AE2" s="1" t="s">
+      <c r="AC2" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="AF2" s="1" t="s">
+      <c r="AD2" s="1" t="s">
         <v>97</v>
       </c>
+      <c r="AE2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AF2" s="2" t="s">
+        <v>99</v>
+      </c>
       <c r="AG2" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AH2" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AJ2" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK2" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AL2" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AM2" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AN2" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AO2" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AP2" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AQ2" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AR2" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AS2" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AT2" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AU2" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AV2" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AW2" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AX2" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AY2" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AZ2" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="BA2" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="BB2" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="BC2" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="BD2" s="1" t="s">
+      <c r="BB2" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="BE2" s="1" t="s">
+      <c r="BC2" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="BF2" s="2" t="s">
+      <c r="BD2" s="2" t="s">
         <v>123</v>
       </c>
+      <c r="BE2" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="BF2" s="1" t="s">
+        <v>125</v>
+      </c>
       <c r="BG2" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="BH2" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
+      </c>
+      <c r="BH2" s="2" t="s">
+        <v>127</v>
       </c>
       <c r="BI2" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="BJ2" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BK2" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="BL2" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="BM2" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="BN2" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
+      </c>
+      <c r="BO2" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="BP2" s="1" t="s">
+        <v>135</v>
       </c>
     </row>
-    <row r="5" spans="51:51">
-      <c r="AY5" s="3"/>
+    <row r="5" spans="53:53">
+      <c r="BA5" s="3"/>
     </row>
-    <row r="6" spans="51:51">
-      <c r="AY6" s="3"/>
+    <row r="6" spans="53:53">
+      <c r="BA6" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetail.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetail.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12540"/>
+    <workbookView windowWidth="28125" windowHeight="11940"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -14,18 +14,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="136">
-  <si>
-    <t>spu</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="132">
   <si>
     <t>sku</t>
   </si>
   <si>
-    <t>一级类目</t>
-  </si>
-  <si>
-    <t>二级类目</t>
+    <t>产品分类</t>
   </si>
   <si>
     <t>销售方式</t>
@@ -220,16 +214,10 @@
     <t>错误信息</t>
   </si>
   <si>
-    <t>{.spuNo}</t>
-  </si>
-  <si>
     <t>{.skuNo}</t>
   </si>
   <si>
-    <t>{.mainCategory}</t>
-  </si>
-  <si>
-    <t>{.secondaryCategory}</t>
+    <t>{.category}</t>
   </si>
   <si>
     <t>{.saleMethod}</t>
@@ -1409,42 +1397,42 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BP6"/>
+  <dimension ref="A1:BN6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
   <cols>
-    <col min="18" max="18" width="11.5" customWidth="1"/>
-    <col min="19" max="19" width="13" customWidth="1"/>
-    <col min="20" max="20" width="11" customWidth="1"/>
-    <col min="21" max="21" width="13.25" customWidth="1"/>
-    <col min="22" max="22" width="9.625" customWidth="1"/>
-    <col min="23" max="23" width="9.375" customWidth="1"/>
-    <col min="24" max="24" width="16" customWidth="1"/>
-    <col min="25" max="25" width="14.875" customWidth="1"/>
-    <col min="26" max="26" width="12" customWidth="1"/>
-    <col min="27" max="27" width="12.375" customWidth="1"/>
-    <col min="28" max="28" width="12.125" customWidth="1"/>
-    <col min="29" max="29" width="12.25" customWidth="1"/>
-    <col min="33" max="33" width="12.25" customWidth="1"/>
-    <col min="34" max="34" width="11.125" customWidth="1"/>
-    <col min="35" max="36" width="8.125" customWidth="1"/>
-    <col min="37" max="38" width="9.25" customWidth="1"/>
-    <col min="39" max="39" width="10.875" customWidth="1"/>
-    <col min="54" max="54" width="7.125" customWidth="1"/>
-    <col min="55" max="55" width="13" customWidth="1"/>
-    <col min="56" max="56" width="11.125" customWidth="1"/>
-    <col min="57" max="57" width="14.5" customWidth="1"/>
-    <col min="58" max="58" width="11.25" customWidth="1"/>
-    <col min="59" max="59" width="14.125" customWidth="1"/>
-    <col min="60" max="60" width="14.875" customWidth="1"/>
-    <col min="61" max="61" width="12.375" customWidth="1"/>
-    <col min="63" max="63" width="10.75" customWidth="1"/>
-    <col min="64" max="64" width="10.625" customWidth="1"/>
-    <col min="65" max="67" width="11.125" customWidth="1"/>
-    <col min="68" max="68" width="34.125" customWidth="1"/>
+    <col min="16" max="16" width="11.5" customWidth="1"/>
+    <col min="17" max="17" width="13" customWidth="1"/>
+    <col min="18" max="18" width="11" customWidth="1"/>
+    <col min="19" max="19" width="13.25" customWidth="1"/>
+    <col min="20" max="20" width="9.625" customWidth="1"/>
+    <col min="21" max="21" width="9.375" customWidth="1"/>
+    <col min="22" max="22" width="16" customWidth="1"/>
+    <col min="23" max="23" width="14.875" customWidth="1"/>
+    <col min="24" max="24" width="12" customWidth="1"/>
+    <col min="25" max="25" width="12.375" customWidth="1"/>
+    <col min="26" max="26" width="12.125" customWidth="1"/>
+    <col min="27" max="27" width="12.25" customWidth="1"/>
+    <col min="31" max="31" width="12.25" customWidth="1"/>
+    <col min="32" max="32" width="11.125" customWidth="1"/>
+    <col min="33" max="34" width="8.125" customWidth="1"/>
+    <col min="35" max="36" width="9.25" customWidth="1"/>
+    <col min="37" max="37" width="10.875" customWidth="1"/>
+    <col min="52" max="52" width="7.125" customWidth="1"/>
+    <col min="53" max="53" width="13" customWidth="1"/>
+    <col min="54" max="54" width="11.125" customWidth="1"/>
+    <col min="55" max="55" width="14.5" customWidth="1"/>
+    <col min="56" max="56" width="11.25" customWidth="1"/>
+    <col min="57" max="57" width="14.125" customWidth="1"/>
+    <col min="58" max="58" width="14.875" customWidth="1"/>
+    <col min="59" max="59" width="12.375" customWidth="1"/>
+    <col min="61" max="61" width="10.75" customWidth="1"/>
+    <col min="62" max="62" width="10.625" customWidth="1"/>
+    <col min="63" max="65" width="11.125" customWidth="1"/>
+    <col min="66" max="66" width="34.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:68">
-      <c r="A1" t="s">
+    <row r="1" customFormat="1" spans="1:66">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -1639,227 +1627,215 @@
       <c r="BM1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="BN1" s="1" t="s">
+      <c r="BN1" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="BO1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:66">
+      <c r="A2" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="BP1" s="4" t="s">
+      <c r="B2" s="1" t="s">
         <v>67</v>
       </c>
+      <c r="C2" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="AC2" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="AD2" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AE2" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="AF2" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="AG2" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="AH2" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="AI2" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="AJ2" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="AK2" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="AL2" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="AM2" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="AN2" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AO2" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AP2" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="AQ2" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="AR2" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="AS2" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="AT2" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="AU2" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="AV2" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="AW2" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="AX2" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="AY2" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="AZ2" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="BA2" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="BB2" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="BC2" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="BD2" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="BE2" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="BF2" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="BG2" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="BH2" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="BI2" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="BJ2" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="BK2" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="BL2" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="BM2" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="BN2" s="1" t="s">
+        <v>131</v>
+      </c>
     </row>
-    <row r="2" spans="1:68">
-      <c r="A2" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="Z2" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="AA2" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="AC2" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="AD2" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="AE2" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="AF2" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="AG2" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="AH2" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="AI2" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="AJ2" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="AK2" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="AL2" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="AM2" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="AN2" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="AO2" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="AP2" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="AQ2" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="AR2" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="AS2" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="AT2" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="AU2" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="AV2" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="AW2" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="AX2" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="AY2" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="AZ2" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="BA2" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="BB2" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="BC2" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="BD2" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BE2" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="BF2" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="BG2" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="BH2" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="BI2" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="BJ2" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="BK2" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="BL2" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="BM2" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="BN2" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="BO2" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="BP2" s="1" t="s">
-        <v>135</v>
-      </c>
+    <row r="5" spans="51:51">
+      <c r="AY5" s="3"/>
     </row>
-    <row r="5" spans="53:53">
-      <c r="BA5" s="3"/>
-    </row>
-    <row r="6" spans="53:53">
-      <c r="BA6" s="3"/>
+    <row r="6" spans="51:51">
+      <c r="AY6" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetail.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetail.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="11940"/>
+    <workbookView windowWidth="28125" windowHeight="12540"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -14,12 +14,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="136">
+  <si>
+    <t>spu</t>
+  </si>
   <si>
     <t>sku</t>
   </si>
   <si>
-    <t>产品分类</t>
+    <t>一级分类</t>
+  </si>
+  <si>
+    <t>二级分类</t>
   </si>
   <si>
     <t>销售方式</t>
@@ -214,10 +220,16 @@
     <t>错误信息</t>
   </si>
   <si>
+    <t>{.spuNo}</t>
+  </si>
+  <si>
     <t>{.skuNo}</t>
   </si>
   <si>
-    <t>{.category}</t>
+    <t>{.mainCategory}</t>
+  </si>
+  <si>
+    <t>{.secondaryCategory}</t>
   </si>
   <si>
     <t>{.saleMethod}</t>
@@ -1397,41 +1409,41 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BN6"/>
+  <dimension ref="A1:BP6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
   <cols>
-    <col min="16" max="16" width="11.5" customWidth="1"/>
-    <col min="17" max="17" width="13" customWidth="1"/>
-    <col min="18" max="18" width="11" customWidth="1"/>
-    <col min="19" max="19" width="13.25" customWidth="1"/>
-    <col min="20" max="20" width="9.625" customWidth="1"/>
-    <col min="21" max="21" width="9.375" customWidth="1"/>
-    <col min="22" max="22" width="16" customWidth="1"/>
-    <col min="23" max="23" width="14.875" customWidth="1"/>
-    <col min="24" max="24" width="12" customWidth="1"/>
-    <col min="25" max="25" width="12.375" customWidth="1"/>
-    <col min="26" max="26" width="12.125" customWidth="1"/>
-    <col min="27" max="27" width="12.25" customWidth="1"/>
-    <col min="31" max="31" width="12.25" customWidth="1"/>
-    <col min="32" max="32" width="11.125" customWidth="1"/>
-    <col min="33" max="34" width="8.125" customWidth="1"/>
-    <col min="35" max="36" width="9.25" customWidth="1"/>
-    <col min="37" max="37" width="10.875" customWidth="1"/>
-    <col min="52" max="52" width="7.125" customWidth="1"/>
-    <col min="53" max="53" width="13" customWidth="1"/>
-    <col min="54" max="54" width="11.125" customWidth="1"/>
-    <col min="55" max="55" width="14.5" customWidth="1"/>
-    <col min="56" max="56" width="11.25" customWidth="1"/>
-    <col min="57" max="57" width="14.125" customWidth="1"/>
-    <col min="58" max="58" width="14.875" customWidth="1"/>
-    <col min="59" max="59" width="12.375" customWidth="1"/>
-    <col min="61" max="61" width="10.75" customWidth="1"/>
-    <col min="62" max="62" width="10.625" customWidth="1"/>
-    <col min="63" max="65" width="11.125" customWidth="1"/>
-    <col min="66" max="66" width="34.125" customWidth="1"/>
+    <col min="18" max="18" width="11.5" customWidth="1"/>
+    <col min="19" max="19" width="13" customWidth="1"/>
+    <col min="20" max="20" width="11" customWidth="1"/>
+    <col min="21" max="21" width="13.25" customWidth="1"/>
+    <col min="22" max="22" width="9.625" customWidth="1"/>
+    <col min="23" max="23" width="9.375" customWidth="1"/>
+    <col min="24" max="24" width="16" customWidth="1"/>
+    <col min="25" max="25" width="14.875" customWidth="1"/>
+    <col min="26" max="26" width="12" customWidth="1"/>
+    <col min="27" max="27" width="12.375" customWidth="1"/>
+    <col min="28" max="28" width="12.125" customWidth="1"/>
+    <col min="29" max="29" width="12.25" customWidth="1"/>
+    <col min="33" max="33" width="12.25" customWidth="1"/>
+    <col min="34" max="34" width="11.125" customWidth="1"/>
+    <col min="35" max="36" width="8.125" customWidth="1"/>
+    <col min="37" max="38" width="9.25" customWidth="1"/>
+    <col min="39" max="39" width="10.875" customWidth="1"/>
+    <col min="54" max="54" width="7.125" customWidth="1"/>
+    <col min="55" max="55" width="13" customWidth="1"/>
+    <col min="56" max="56" width="11.125" customWidth="1"/>
+    <col min="57" max="57" width="14.5" customWidth="1"/>
+    <col min="58" max="58" width="11.25" customWidth="1"/>
+    <col min="59" max="59" width="14.125" customWidth="1"/>
+    <col min="60" max="60" width="14.875" customWidth="1"/>
+    <col min="61" max="61" width="12.375" customWidth="1"/>
+    <col min="63" max="63" width="10.75" customWidth="1"/>
+    <col min="64" max="64" width="10.625" customWidth="1"/>
+    <col min="65" max="67" width="11.125" customWidth="1"/>
+    <col min="68" max="68" width="34.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:66">
+    <row r="1" customFormat="1" spans="1:68">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1627,215 +1639,227 @@
       <c r="BM1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="BN1" s="4" t="s">
+      <c r="BN1" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="BO1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="BP1" s="4" t="s">
+        <v>67</v>
+      </c>
     </row>
-    <row r="2" spans="1:66">
+    <row r="2" spans="1:68">
       <c r="A2" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>80</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>82</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="AC2" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="AD2" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="AE2" s="1" t="s">
+      <c r="AC2" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="AF2" s="1" t="s">
+      <c r="AD2" s="1" t="s">
         <v>97</v>
       </c>
+      <c r="AE2" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AF2" s="2" t="s">
+        <v>99</v>
+      </c>
       <c r="AG2" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AH2" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AJ2" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK2" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AL2" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AM2" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AN2" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AO2" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AP2" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AQ2" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AR2" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AS2" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AT2" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AU2" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AV2" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AW2" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AX2" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AY2" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AZ2" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="BA2" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="BB2" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="BC2" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="BD2" s="1" t="s">
+      <c r="BB2" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="BE2" s="1" t="s">
+      <c r="BC2" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="BF2" s="2" t="s">
+      <c r="BD2" s="2" t="s">
         <v>123</v>
       </c>
+      <c r="BE2" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="BF2" s="1" t="s">
+        <v>125</v>
+      </c>
       <c r="BG2" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="BH2" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
+      </c>
+      <c r="BH2" s="2" t="s">
+        <v>127</v>
       </c>
       <c r="BI2" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="BJ2" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BK2" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="BL2" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="BM2" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="BN2" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
+      </c>
+      <c r="BO2" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="BP2" s="1" t="s">
+        <v>135</v>
       </c>
     </row>
-    <row r="5" spans="51:51">
-      <c r="AY5" s="3"/>
+    <row r="5" spans="53:53">
+      <c r="BA5" s="3"/>
     </row>
-    <row r="6" spans="51:51">
-      <c r="AY6" s="3"/>
+    <row r="6" spans="53:53">
+      <c r="BA6" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetail.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetail.xlsx
@@ -40,7 +40,7 @@
     <t>产品用途</t>
   </si>
   <si>
-    <t>存在侵权风险</t>
+    <t>存在侵权风险(是/否)</t>
   </si>
   <si>
     <t>主要材质</t>
@@ -82,13 +82,13 @@
     <t>标准零售价</t>
   </si>
   <si>
-    <t>目标毛利率</t>
-  </si>
-  <si>
-    <t>实际毛利率(人民币)</t>
-  </si>
-  <si>
-    <t>实际毛利率(美元)</t>
+    <t>目标毛利率%</t>
+  </si>
+  <si>
+    <t>实际毛利率%(人民币)</t>
+  </si>
+  <si>
+    <t>实际毛利率%(美元)</t>
   </si>
   <si>
     <t>年目标销售量</t>
@@ -133,7 +133,7 @@
     <t>报关申报价格</t>
   </si>
   <si>
-    <t>海关编码</t>
+    <t>中国海关编码</t>
   </si>
   <si>
     <t>申报要素</t>
@@ -1412,12 +1412,13 @@
   <dimension ref="A1:BP6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
   <cols>
+    <col min="9" max="9" width="18.25" customWidth="1"/>
     <col min="18" max="18" width="11.5" customWidth="1"/>
     <col min="19" max="19" width="13" customWidth="1"/>
     <col min="20" max="20" width="11" customWidth="1"/>
     <col min="21" max="21" width="13.25" customWidth="1"/>
     <col min="22" max="22" width="9.625" customWidth="1"/>
-    <col min="23" max="23" width="9.375" customWidth="1"/>
+    <col min="23" max="23" width="10.25" customWidth="1"/>
     <col min="24" max="24" width="16" customWidth="1"/>
     <col min="25" max="25" width="14.875" customWidth="1"/>
     <col min="26" max="26" width="12" customWidth="1"/>
@@ -1428,7 +1429,7 @@
     <col min="34" max="34" width="11.125" customWidth="1"/>
     <col min="35" max="36" width="8.125" customWidth="1"/>
     <col min="37" max="38" width="9.25" customWidth="1"/>
-    <col min="39" max="39" width="10.875" customWidth="1"/>
+    <col min="39" max="40" width="10.875" customWidth="1"/>
     <col min="54" max="54" width="7.125" customWidth="1"/>
     <col min="55" max="55" width="13" customWidth="1"/>
     <col min="56" max="56" width="11.125" customWidth="1"/>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetail.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetail.xlsx
@@ -4,17 +4,30 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12540"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="140">
   <si>
     <t>spu</t>
   </si>
@@ -52,6 +65,12 @@
     <t>品名（英文）</t>
   </si>
   <si>
+    <t>产品类型</t>
+  </si>
+  <si>
+    <t>迭代产品</t>
+  </si>
+  <si>
     <t>品牌</t>
   </si>
   <si>
@@ -254,6 +273,12 @@
   </si>
   <si>
     <t>{.nameEn}</t>
+  </si>
+  <si>
+    <t>{.typeName}</t>
+  </si>
+  <si>
+    <t>{.iterateRefSkuNo}</t>
   </si>
   <si>
     <t>{.brandName}</t>
@@ -427,7 +452,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -465,34 +490,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -509,6 +506,45 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -518,41 +554,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -603,7 +607,28 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -618,49 +643,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -672,121 +781,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -823,21 +848,6 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -871,6 +881,21 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -929,148 +954,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1093,52 +1118,52 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1409,42 +1434,44 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BP6"/>
+  <dimension ref="A1:BR6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
   <cols>
     <col min="9" max="9" width="18.25" customWidth="1"/>
-    <col min="18" max="18" width="11.5" customWidth="1"/>
-    <col min="19" max="19" width="13" customWidth="1"/>
-    <col min="20" max="20" width="11" customWidth="1"/>
-    <col min="21" max="21" width="13.25" customWidth="1"/>
-    <col min="22" max="22" width="9.625" customWidth="1"/>
-    <col min="23" max="23" width="10.25" customWidth="1"/>
-    <col min="24" max="24" width="16" customWidth="1"/>
-    <col min="25" max="25" width="14.875" customWidth="1"/>
-    <col min="26" max="26" width="12" customWidth="1"/>
-    <col min="27" max="27" width="12.375" customWidth="1"/>
-    <col min="28" max="28" width="12.125" customWidth="1"/>
-    <col min="29" max="29" width="12.25" customWidth="1"/>
-    <col min="33" max="33" width="12.25" customWidth="1"/>
-    <col min="34" max="34" width="11.125" customWidth="1"/>
-    <col min="35" max="36" width="8.125" customWidth="1"/>
-    <col min="37" max="38" width="9.25" customWidth="1"/>
-    <col min="39" max="40" width="10.875" customWidth="1"/>
-    <col min="54" max="54" width="7.125" customWidth="1"/>
-    <col min="55" max="55" width="13" customWidth="1"/>
-    <col min="56" max="56" width="11.125" customWidth="1"/>
-    <col min="57" max="57" width="14.5" customWidth="1"/>
-    <col min="58" max="58" width="11.25" customWidth="1"/>
-    <col min="59" max="59" width="14.125" customWidth="1"/>
-    <col min="60" max="60" width="14.875" customWidth="1"/>
-    <col min="61" max="61" width="12.375" customWidth="1"/>
-    <col min="63" max="63" width="10.75" customWidth="1"/>
-    <col min="64" max="64" width="10.625" customWidth="1"/>
-    <col min="65" max="67" width="11.125" customWidth="1"/>
-    <col min="68" max="68" width="34.125" customWidth="1"/>
+    <col min="13" max="13" width="10.375" customWidth="1"/>
+    <col min="14" max="14" width="16" customWidth="1"/>
+    <col min="20" max="20" width="11.5" customWidth="1"/>
+    <col min="21" max="21" width="13" customWidth="1"/>
+    <col min="22" max="22" width="11" customWidth="1"/>
+    <col min="23" max="23" width="13.25" customWidth="1"/>
+    <col min="24" max="24" width="9.625" customWidth="1"/>
+    <col min="25" max="25" width="10.25" customWidth="1"/>
+    <col min="26" max="26" width="16" customWidth="1"/>
+    <col min="27" max="27" width="14.875" customWidth="1"/>
+    <col min="28" max="28" width="12" customWidth="1"/>
+    <col min="29" max="29" width="12.375" customWidth="1"/>
+    <col min="30" max="30" width="12.125" customWidth="1"/>
+    <col min="31" max="31" width="12.25" customWidth="1"/>
+    <col min="35" max="35" width="12.25" customWidth="1"/>
+    <col min="36" max="36" width="11.125" customWidth="1"/>
+    <col min="37" max="38" width="8.125" customWidth="1"/>
+    <col min="39" max="40" width="9.25" customWidth="1"/>
+    <col min="41" max="42" width="10.875" customWidth="1"/>
+    <col min="56" max="56" width="7.125" customWidth="1"/>
+    <col min="57" max="57" width="13" customWidth="1"/>
+    <col min="58" max="58" width="11.125" customWidth="1"/>
+    <col min="59" max="59" width="14.5" customWidth="1"/>
+    <col min="60" max="60" width="11.25" customWidth="1"/>
+    <col min="61" max="61" width="14.125" customWidth="1"/>
+    <col min="62" max="62" width="14.875" customWidth="1"/>
+    <col min="63" max="63" width="12.375" customWidth="1"/>
+    <col min="65" max="65" width="10.75" customWidth="1"/>
+    <col min="66" max="66" width="10.625" customWidth="1"/>
+    <col min="67" max="69" width="11.125" customWidth="1"/>
+    <col min="70" max="70" width="34.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:68">
+    <row r="1" customFormat="1" spans="1:70">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1646,221 +1673,233 @@
       <c r="BO1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="BP1" s="4" t="s">
+      <c r="BP1" s="1" t="s">
         <v>67</v>
       </c>
+      <c r="BQ1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="BR1" s="4" t="s">
+        <v>69</v>
+      </c>
     </row>
-    <row r="2" spans="1:68">
+    <row r="2" spans="1:70">
       <c r="A2" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>86</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AD2" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="AE2" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="AF2" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="AG2" s="1" t="s">
+      <c r="AE2" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="AH2" s="1" t="s">
+      <c r="AF2" s="1" t="s">
         <v>101</v>
       </c>
+      <c r="AG2" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AH2" s="2" t="s">
+        <v>103</v>
+      </c>
       <c r="AI2" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AJ2" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AK2" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AL2" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AM2" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AN2" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AO2" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AP2" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AQ2" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AR2" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AS2" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AT2" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AU2" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AV2" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AW2" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AX2" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="AY2" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="AZ2" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="BA2" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="BB2" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="BC2" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="BD2" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="BE2" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="BF2" s="1" t="s">
+      <c r="BD2" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="BG2" s="1" t="s">
+      <c r="BE2" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="BH2" s="2" t="s">
+      <c r="BF2" s="2" t="s">
         <v>127</v>
       </c>
+      <c r="BG2" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="BH2" s="1" t="s">
+        <v>129</v>
+      </c>
       <c r="BI2" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="BJ2" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
+      </c>
+      <c r="BJ2" s="2" t="s">
+        <v>131</v>
       </c>
       <c r="BK2" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="BL2" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="BM2" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="BN2" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="BO2" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="BP2" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
+      </c>
+      <c r="BQ2" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="BR2" s="1" t="s">
+        <v>139</v>
       </c>
     </row>
-    <row r="5" spans="53:53">
-      <c r="BA5" s="3"/>
+    <row r="5" spans="55:55">
+      <c r="BC5" s="3"/>
     </row>
-    <row r="6" spans="53:53">
-      <c r="BA6" s="3"/>
+    <row r="6" spans="55:55">
+      <c r="BC6" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetail.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetail.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="23130" windowHeight="11850"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="144">
   <si>
     <t>spu</t>
   </si>
@@ -236,6 +236,12 @@
     <t>产品开发状态</t>
   </si>
   <si>
+    <t>推荐仓位(小货区)</t>
+  </si>
+  <si>
+    <t>推荐仓位(大货区)</t>
+  </si>
+  <si>
     <t>错误信息</t>
   </si>
   <si>
@@ -444,6 +450,12 @@
   </si>
   <si>
     <t>{.productStateName}</t>
+  </si>
+  <si>
+    <t>{.warehouseLocation}</t>
+  </si>
+  <si>
+    <t>{.warehouseLocationLarge}</t>
   </si>
   <si>
     <t>{.errorMsg}</t>
@@ -1434,7 +1446,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BR6"/>
+  <dimension ref="A1:BT6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
   <cols>
     <col min="9" max="9" width="18.25" customWidth="1"/>
@@ -1467,11 +1479,11 @@
     <col min="63" max="63" width="12.375" customWidth="1"/>
     <col min="65" max="65" width="10.75" customWidth="1"/>
     <col min="66" max="66" width="10.625" customWidth="1"/>
-    <col min="67" max="69" width="11.125" customWidth="1"/>
-    <col min="70" max="70" width="34.125" customWidth="1"/>
+    <col min="67" max="71" width="11.125" customWidth="1"/>
+    <col min="72" max="72" width="34.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:70">
+    <row r="1" customFormat="1" spans="1:72">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1679,220 +1691,232 @@
       <c r="BQ1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="BR1" s="4" t="s">
+      <c r="BR1" s="1" t="s">
         <v>69</v>
       </c>
+      <c r="BS1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="BT1" s="4" t="s">
+        <v>71</v>
+      </c>
     </row>
-    <row r="2" spans="1:70">
+    <row r="2" spans="1:72">
       <c r="A2" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AD2" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AE2" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AF2" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AJ2" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AK2" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="AL2" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AM2" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="AN2" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AO2" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="AP2" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AQ2" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="AR2" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AS2" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AT2" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AU2" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AV2" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="AW2" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="AX2" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="AY2" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="AZ2" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="BA2" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="BB2" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="BC2" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="BD2" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="BE2" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="BH2" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="BI2" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="BK2" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="BL2" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="BM2" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="BN2" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="BO2" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="BP2" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="BQ2" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="BR2" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
+      </c>
+      <c r="BS2" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="BT2" s="1" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="55:55">

--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetail.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetail.xlsx
@@ -1111,10 +1111,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1122,6 +1125,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1479,451 +1485,452 @@
     <col min="63" max="63" width="12.375" customWidth="1"/>
     <col min="65" max="65" width="10.75" customWidth="1"/>
     <col min="66" max="66" width="10.625" customWidth="1"/>
-    <col min="67" max="71" width="11.125" customWidth="1"/>
+    <col min="67" max="69" width="11.125" customWidth="1"/>
+    <col min="70" max="71" width="11.125" style="1" customWidth="1"/>
     <col min="72" max="72" width="34.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" spans="1:72">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AC1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AD1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AE1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AF1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AG1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AH1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AI1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AK1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AL1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AM1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AN1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AO1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AP1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AQ1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AR1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AS1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AT1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AU1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AV1" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AW1" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AX1" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="AY1" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="AZ1" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BA1" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="BB1" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" s="1" t="s">
+      <c r="BC1" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" s="1" t="s">
+      <c r="BD1" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" s="1" t="s">
+      <c r="BE1" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" s="1" t="s">
+      <c r="BF1" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="BG1" s="1" t="s">
+      <c r="BG1" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="BH1" s="1" t="s">
+      <c r="BH1" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="BI1" s="1" t="s">
+      <c r="BI1" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="BJ1" s="1" t="s">
+      <c r="BJ1" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="BK1" s="1" t="s">
+      <c r="BK1" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="BL1" s="1" t="s">
+      <c r="BL1" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="BM1" s="1" t="s">
+      <c r="BM1" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="BN1" s="1" t="s">
+      <c r="BN1" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="BO1" s="1" t="s">
+      <c r="BO1" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="BP1" s="1" t="s">
+      <c r="BP1" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="BQ1" s="1" t="s">
+      <c r="BQ1" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="BR1" s="1" t="s">
+      <c r="BR1" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="BS1" s="1" t="s">
+      <c r="BS1" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="BT1" s="4" t="s">
+      <c r="BT1" s="6" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:72">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="N2" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="O2" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="P2" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="Q2" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="R2" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="S2" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="T2" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="U2" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="V2" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="W2" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="X2" s="1" t="s">
+      <c r="X2" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="Y2" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="Z2" s="1" t="s">
+      <c r="Z2" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="AA2" s="1" t="s">
+      <c r="AA2" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="AB2" s="1" t="s">
+      <c r="AB2" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="AC2" s="1" t="s">
+      <c r="AC2" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="AD2" s="1" t="s">
+      <c r="AD2" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="AE2" s="1" t="s">
+      <c r="AE2" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="AF2" s="1" t="s">
+      <c r="AF2" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="AG2" s="2" t="s">
+      <c r="AG2" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="AH2" s="2" t="s">
+      <c r="AH2" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="AI2" s="1" t="s">
+      <c r="AI2" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="AJ2" s="1" t="s">
+      <c r="AJ2" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="AK2" s="1" t="s">
+      <c r="AK2" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="AL2" s="1" t="s">
+      <c r="AL2" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="AM2" s="1" t="s">
+      <c r="AM2" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="AN2" s="1" t="s">
+      <c r="AN2" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="AO2" s="1" t="s">
+      <c r="AO2" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="AP2" s="1" t="s">
+      <c r="AP2" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="AQ2" s="1" t="s">
+      <c r="AQ2" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="AR2" s="1" t="s">
+      <c r="AR2" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="AS2" s="1" t="s">
+      <c r="AS2" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="AT2" s="1" t="s">
+      <c r="AT2" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="AU2" s="1" t="s">
+      <c r="AU2" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="AV2" s="1" t="s">
+      <c r="AV2" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="AW2" s="1" t="s">
+      <c r="AW2" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="AX2" s="1" t="s">
+      <c r="AX2" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="AY2" s="1" t="s">
+      <c r="AY2" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="AZ2" s="1" t="s">
+      <c r="AZ2" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="BA2" s="1" t="s">
+      <c r="BA2" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="BB2" s="1" t="s">
+      <c r="BB2" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="BC2" s="1" t="s">
+      <c r="BC2" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="BD2" s="1" t="s">
+      <c r="BD2" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="BE2" s="1" t="s">
+      <c r="BE2" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="BF2" s="2" t="s">
+      <c r="BF2" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="BG2" s="2" t="s">
+      <c r="BG2" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="BH2" s="1" t="s">
+      <c r="BH2" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="BI2" s="1" t="s">
+      <c r="BI2" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="BJ2" s="2" t="s">
+      <c r="BJ2" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="BK2" s="1" t="s">
+      <c r="BK2" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="BL2" s="1" t="s">
+      <c r="BL2" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="BM2" s="1" t="s">
+      <c r="BM2" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="BN2" s="1" t="s">
+      <c r="BN2" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="BO2" s="1" t="s">
+      <c r="BO2" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="BP2" s="1" t="s">
+      <c r="BP2" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="BQ2" s="1" t="s">
+      <c r="BQ2" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="BR2" s="1" t="s">
+      <c r="BR2" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="BS2" s="1" t="s">
+      <c r="BS2" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="BT2" s="1" t="s">
+      <c r="BT2" s="2" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="5" spans="55:55">
-      <c r="BC5" s="3"/>
+      <c r="BC5" s="4"/>
     </row>
     <row r="6" spans="55:55">
-      <c r="BC6" s="3"/>
+      <c r="BC6" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetail.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetail.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23130" windowHeight="11850"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -27,21 +27,347 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="168">
   <si>
     <t>spu</t>
   </si>
   <si>
-    <t>sku</t>
-  </si>
-  <si>
-    <t>一级分类</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>sku编号</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>一级分类</t>
+    </r>
   </si>
   <si>
     <t>二级分类</t>
   </si>
   <si>
-    <t>销售方式</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>应用分类</t>
+    </r>
+  </si>
+  <si>
+    <t>产品经理</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>销售方式</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>品名</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>品名（英文）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>产品类型</t>
+    </r>
+  </si>
+  <si>
+    <t>迭代产品</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>产品属性</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>品牌</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>产品开发状态</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>产品等级</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>销售渠道</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是否客户定制</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>模具成本(￥)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>委托开发成本(￥)</t>
+    </r>
   </si>
   <si>
     <t>产品卖点</t>
@@ -53,94 +379,611 @@
     <t>产品用途</t>
   </si>
   <si>
+    <t>计划上市时间</t>
+  </si>
+  <si>
     <t>存在侵权风险(是/否)</t>
   </si>
   <si>
+    <t>单位</t>
+  </si>
+  <si>
     <t>主要材质</t>
   </si>
   <si>
-    <t>品名</t>
-  </si>
-  <si>
-    <t>品名（英文）</t>
-  </si>
-  <si>
-    <t>产品类型</t>
-  </si>
-  <si>
-    <t>迭代产品</t>
-  </si>
-  <si>
-    <t>品牌</t>
-  </si>
-  <si>
-    <t>产品属性</t>
-  </si>
-  <si>
-    <t>计划上市时间</t>
-  </si>
-  <si>
-    <t>单位</t>
-  </si>
-  <si>
-    <t>产品经理</t>
-  </si>
-  <si>
-    <t>目标含税成本</t>
-  </si>
-  <si>
-    <t>目标不含税成本</t>
-  </si>
-  <si>
-    <t>实际含税成本</t>
-  </si>
-  <si>
-    <t>实际不含税成本</t>
-  </si>
-  <si>
-    <t>标准零售价</t>
-  </si>
-  <si>
-    <t>目标毛利率%</t>
-  </si>
-  <si>
-    <t>实际毛利率%(人民币)</t>
-  </si>
-  <si>
-    <t>实际毛利率%(美元)</t>
-  </si>
-  <si>
-    <t>年目标销售量</t>
-  </si>
-  <si>
-    <t>年目标销售额</t>
-  </si>
-  <si>
-    <t>月目标销售量</t>
-  </si>
-  <si>
-    <t>月目标销售额</t>
-  </si>
-  <si>
-    <t>销售国家</t>
-  </si>
-  <si>
-    <t>上市时间</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>预计立项成本</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>￥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>实际量产成本</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>￥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>预计项目成本</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>￥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>税率</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>目标含税成本(￥)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>目标不含税成本</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>￥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>标准零售价(￥)</t>
+    </r>
+  </si>
+  <si>
+    <t>ean码</t>
+  </si>
+  <si>
+    <t>MOQ(最小起订量)</t>
+  </si>
+  <si>
+    <t>试产数量</t>
+  </si>
+  <si>
+    <t>首批量产数量</t>
+  </si>
+  <si>
+    <t>计划首批下单量</t>
+  </si>
+  <si>
+    <t>实际首批到货量</t>
+  </si>
+  <si>
+    <t>预计首批到货时间</t>
+  </si>
+  <si>
+    <t>实际首批到货时间</t>
+  </si>
+  <si>
+    <t>首批下单时间</t>
+  </si>
+  <si>
+    <t>交货周期(天)</t>
+  </si>
+  <si>
+    <t>采购员</t>
+  </si>
+  <si>
+    <t>首批到货状态</t>
+  </si>
+  <si>
+    <t>一级供应商</t>
+  </si>
+  <si>
+    <t>二级供应商</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>年目标销量</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>年目标销售额（￥）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>目标月销售量</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>目标月销售额（￥）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>首季度目标销量</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>销售国家</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>图片是否完成</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>视频是否完成</t>
+    </r>
   </si>
   <si>
     <t>退市时间</t>
   </si>
   <si>
-    <t>图片是否完成</t>
-  </si>
-  <si>
-    <t>视频是否完成</t>
-  </si>
-  <si>
-    <t>销售状态</t>
-  </si>
-  <si>
-    <t>报关产品属性</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>销售状态</t>
+    </r>
+  </si>
+  <si>
+    <t>产品上市(含培训)资料链接</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是否可销售</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>销售平台</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">报关产品属性
+</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>保险属性</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>报关申报价（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="Helvetica"/>
+        <charset val="134"/>
+      </rPr>
+      <t>$</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
   </si>
   <si>
     <t>报关中文名</t>
@@ -149,12 +992,23 @@
     <t>报关英文名</t>
   </si>
   <si>
-    <t>报关申报价格</t>
-  </si>
-  <si>
     <t>中国海关编码</t>
   </si>
   <si>
+    <t>报关型号</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color indexed="8"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>报关单位</t>
+    </r>
+  </si>
+  <si>
     <t>申报要素</t>
   </si>
   <si>
@@ -173,69 +1027,27 @@
     <t>产品尺寸(高)</t>
   </si>
   <si>
+    <t>箱规(长)</t>
+  </si>
+  <si>
+    <t>箱规(宽)</t>
+  </si>
+  <si>
+    <t>箱规(高)</t>
+  </si>
+  <si>
     <t>毛重</t>
   </si>
   <si>
     <t>净重</t>
   </si>
   <si>
-    <t>箱规(长)</t>
-  </si>
-  <si>
-    <t>箱规(宽)</t>
-  </si>
-  <si>
-    <t>箱规(高)</t>
-  </si>
-  <si>
     <t>单箱重量</t>
   </si>
   <si>
     <t>单箱数量</t>
   </si>
   <si>
-    <t>ean码</t>
-  </si>
-  <si>
-    <t>计划首批下单量</t>
-  </si>
-  <si>
-    <t>首批下单时间</t>
-  </si>
-  <si>
-    <t>预计首批到货时间</t>
-  </si>
-  <si>
-    <t>MOQ(最小起订量)</t>
-  </si>
-  <si>
-    <t>交货周期(天)</t>
-  </si>
-  <si>
-    <t>实际首批到货时间</t>
-  </si>
-  <si>
-    <t>实际首批到货量</t>
-  </si>
-  <si>
-    <t>首批到货状态</t>
-  </si>
-  <si>
-    <t>采购员</t>
-  </si>
-  <si>
-    <t>一级供应商</t>
-  </si>
-  <si>
-    <t>二级供应商</t>
-  </si>
-  <si>
-    <t>量产入库时间</t>
-  </si>
-  <si>
-    <t>产品开发状态</t>
-  </si>
-  <si>
     <t>推荐仓位(小货区)</t>
   </si>
   <si>
@@ -257,9 +1069,51 @@
     <t>{.secondaryCategory}</t>
   </si>
   <si>
+    <t>{.applicationCategoryName}</t>
+  </si>
+  <si>
+    <t>{.chargeName}</t>
+  </si>
+  <si>
     <t>{.saleMethod}</t>
   </si>
   <si>
+    <t>{.name}</t>
+  </si>
+  <si>
+    <t>{.nameEn}</t>
+  </si>
+  <si>
+    <t>{.typeName}</t>
+  </si>
+  <si>
+    <t>{.iterateRefSkuNo}</t>
+  </si>
+  <si>
+    <t>{.property}</t>
+  </si>
+  <si>
+    <t>{.brandName}</t>
+  </si>
+  <si>
+    <t>{.productStateName}</t>
+  </si>
+  <si>
+    <t>{.grade}</t>
+  </si>
+  <si>
+    <t>{.salesChannel}</t>
+  </si>
+  <si>
+    <t>{.isCustomized}</t>
+  </si>
+  <si>
+    <t>{.moldCost}</t>
+  </si>
+  <si>
+    <t>{.entrustedDevelopCost}</t>
+  </si>
+  <si>
     <t>{.sellSpot}</t>
   </si>
   <si>
@@ -269,37 +1123,28 @@
     <t>{.usageDesc}</t>
   </si>
   <si>
+    <t>{.planListingTime}</t>
+  </si>
+  <si>
     <t>{.pirateRisk}</t>
   </si>
   <si>
+    <t>{.unitName}</t>
+  </si>
+  <si>
     <t>{.materials}</t>
   </si>
   <si>
-    <t>{.name}</t>
-  </si>
-  <si>
-    <t>{.nameEn}</t>
-  </si>
-  <si>
-    <t>{.typeName}</t>
-  </si>
-  <si>
-    <t>{.iterateRefSkuNo}</t>
-  </si>
-  <si>
-    <t>{.brandName}</t>
-  </si>
-  <si>
-    <t>{.property}</t>
-  </si>
-  <si>
-    <t>{.planListingTimeStr}</t>
-  </si>
-  <si>
-    <t>{.unitName}</t>
-  </si>
-  <si>
-    <t>{.chargeName}</t>
+    <t>{.projectApprovalCost}</t>
+  </si>
+  <si>
+    <t>{.massCost}</t>
+  </si>
+  <si>
+    <t>{.projectCost}</t>
+  </si>
+  <si>
+    <t>{.taxRate}</t>
   </si>
   <si>
     <t>{.targetTaxCost}</t>
@@ -308,69 +1153,114 @@
     <t>{.targetNoTaxCost}</t>
   </si>
   <si>
-    <t>{.actualTaxCost}</t>
-  </si>
-  <si>
-    <t>{.actualNoTaxCost}</t>
-  </si>
-  <si>
     <t>{.retailPrice}</t>
   </si>
   <si>
-    <t>{.targetGpm}</t>
-  </si>
-  <si>
-    <t>{.actualGpmCny}</t>
-  </si>
-  <si>
-    <t>{.actualGpmUsd}</t>
-  </si>
-  <si>
-    <t>{.yearSaleQtyStr}</t>
-  </si>
-  <si>
-    <t>{.yearSaleAmountStr}</t>
-  </si>
-  <si>
-    <t>{.monthSaleQtyStr}</t>
-  </si>
-  <si>
-    <t>{.monthSaleAmountStr}</t>
+    <t>{.ean}</t>
+  </si>
+  <si>
+    <t>{.moq}</t>
+  </si>
+  <si>
+    <t>{.trialProductionQty}</t>
+  </si>
+  <si>
+    <t>{.firstMassQty}</t>
+  </si>
+  <si>
+    <t>{.planOrderQty}</t>
+  </si>
+  <si>
+    <t>{.actualArrivalQty}</t>
+  </si>
+  <si>
+    <t>{.planArrivalTime}</t>
+  </si>
+  <si>
+    <t>{.actualArrivalTime}</t>
+  </si>
+  <si>
+    <t>{.placeOrderTime}</t>
+  </si>
+  <si>
+    <t>{.deliveryCycle}</t>
+  </si>
+  <si>
+    <t>{.purchaseUser}</t>
+  </si>
+  <si>
+    <t>{.arrivalState}</t>
+  </si>
+  <si>
+    <t>{.mainSupplier}</t>
+  </si>
+  <si>
+    <t>{.secondSupplier}</t>
+  </si>
+  <si>
+    <t>{.yearSaleQty}</t>
+  </si>
+  <si>
+    <t>{.yearSaleAmount}</t>
+  </si>
+  <si>
+    <t>{.monthSaleQty}</t>
+  </si>
+  <si>
+    <t>{.monthSaleAmount}</t>
+  </si>
+  <si>
+    <t>{.targetSalesQty}</t>
   </si>
   <si>
     <t>{.saleCountry}</t>
   </si>
   <si>
-    <t>{.listingTimeStr}</t>
-  </si>
-  <si>
-    <t>{.delistingTimeStr}</t>
-  </si>
-  <si>
     <t>{.isFinishedImg}</t>
   </si>
   <si>
     <t>{.isFinishedVideo}</t>
   </si>
   <si>
+    <t>{.delistingTime}</t>
+  </si>
+  <si>
     <t>{.saleState}</t>
   </si>
   <si>
+    <t>{.dataUrl}</t>
+  </si>
+  <si>
+    <t>{.isMarketable}</t>
+  </si>
+  <si>
+    <t>{.salesPlatform}</t>
+  </si>
+  <si>
     <t>{.productProperty}</t>
   </si>
   <si>
+    <t>{.insuranceProperty}</t>
+  </si>
+  <si>
+    <t>{.declarePrice}</t>
+  </si>
+  <si>
     <t>{.declareChineseName}</t>
   </si>
   <si>
     <t>{.declareEnglishName}</t>
   </si>
   <si>
-    <t>{.declarePriceStr}</t>
-  </si>
-  <si>
     <t>{.customsCode}</t>
   </si>
   <si>
+    <t>{.declareModel}</t>
+  </si>
+  <si>
+    <t>{.declareUnit}</t>
+  </si>
+  <si>
     <t>{.declareElement}</t>
   </si>
   <si>
@@ -380,76 +1270,34 @@
     <t>{.englishUsage}</t>
   </si>
   <si>
-    <t>{.productSizeLengthStr}</t>
-  </si>
-  <si>
-    <t>{.productSizeWideStr}</t>
-  </si>
-  <si>
-    <t>{.productSizeHighStr}</t>
-  </si>
-  <si>
-    <t>{.grossWeightStr}</t>
-  </si>
-  <si>
-    <t>{.netWeightStr}</t>
-  </si>
-  <si>
-    <t>{.boxSizeLengthStr}</t>
-  </si>
-  <si>
-    <t>{.boxSizeWideStr}</t>
-  </si>
-  <si>
-    <t>{.boxSizeHighStr}</t>
-  </si>
-  <si>
-    <t>{.boxWeightStr}</t>
-  </si>
-  <si>
-    <t>{.boxQtyStr}</t>
-  </si>
-  <si>
-    <t>{.ean}</t>
-  </si>
-  <si>
-    <t>{.planOrderQtyStr}</t>
-  </si>
-  <si>
-    <t>{.placeOrderTimeStr}</t>
-  </si>
-  <si>
-    <t>{.planArrivalTimeStr}</t>
-  </si>
-  <si>
-    <t>{.moqStr}</t>
-  </si>
-  <si>
-    <t>{.deliveryCycleStr}</t>
-  </si>
-  <si>
-    <t>{.actualArrivalTimeStr}</t>
-  </si>
-  <si>
-    <t>{.actualArrivalQtyStr}</t>
-  </si>
-  <si>
-    <t>{.arrivalState}</t>
-  </si>
-  <si>
-    <t>{.purchaseUser}</t>
-  </si>
-  <si>
-    <t>{.mainSupplier}</t>
-  </si>
-  <si>
-    <t>{.secondSupplier}</t>
-  </si>
-  <si>
-    <t>{.firstMassProductDateStr}</t>
-  </si>
-  <si>
-    <t>{.productStateName}</t>
+    <t>{.productLength}</t>
+  </si>
+  <si>
+    <t>{.productWidth}</t>
+  </si>
+  <si>
+    <t>{.productHeight}</t>
+  </si>
+  <si>
+    <t>{.boxLength}</t>
+  </si>
+  <si>
+    <t>{.boxWidth}</t>
+  </si>
+  <si>
+    <t>{.boxHeight}</t>
+  </si>
+  <si>
+    <t>{.grossWeight}</t>
+  </si>
+  <si>
+    <t>{.netWeight}</t>
+  </si>
+  <si>
+    <t>{.boxWeight}</t>
+  </si>
+  <si>
+    <t>{.boxQty}</t>
   </si>
   <si>
     <t>{.warehouseLocation}</t>
@@ -465,14 +1313,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="8">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
+    <numFmt numFmtId="176" formatCode="0.0000_ "/>
+    <numFmt numFmtId="177" formatCode="yyyy/mm/dd"/>
+    <numFmt numFmtId="178" formatCode="0_ "/>
+    <numFmt numFmtId="179" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -490,6 +1341,12 @@
     <font>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -645,6 +1502,28 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <name val="Helvetica"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -966,152 +1845,152 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1121,16 +2000,40 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1452,9 +2355,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BT6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
+  <dimension ref="A1:CF4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3"/>
   <cols>
+    <col min="4" max="4" width="23.875" customWidth="1"/>
     <col min="9" max="9" width="18.25" customWidth="1"/>
     <col min="13" max="13" width="10.375" customWidth="1"/>
     <col min="14" max="14" width="16" customWidth="1"/>
@@ -1475,6 +2379,8 @@
     <col min="37" max="38" width="8.125" customWidth="1"/>
     <col min="39" max="40" width="9.25" customWidth="1"/>
     <col min="41" max="42" width="10.875" customWidth="1"/>
+    <col min="50" max="50" width="13.75" customWidth="1"/>
+    <col min="51" max="51" width="11.625" customWidth="1"/>
     <col min="56" max="56" width="7.125" customWidth="1"/>
     <col min="57" max="57" width="13" customWidth="1"/>
     <col min="58" max="58" width="11.125" customWidth="1"/>
@@ -1487,65 +2393,65 @@
     <col min="66" max="66" width="10.625" customWidth="1"/>
     <col min="67" max="69" width="11.125" customWidth="1"/>
     <col min="70" max="71" width="11.125" style="1" customWidth="1"/>
-    <col min="72" max="72" width="34.125" customWidth="1"/>
+    <col min="72" max="72" width="11.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:72">
+    <row r="1" ht="24" spans="1:84">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="5" t="s">
         <v>18</v>
       </c>
       <c r="T1" s="2" t="s">
@@ -1557,7 +2463,7 @@
       <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="W1" s="6" t="s">
         <v>22</v>
       </c>
       <c r="X1" s="2" t="s">
@@ -1569,55 +2475,55 @@
       <c r="Z1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AA1" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AB1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AC1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AD1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AE1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AF1" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AG1" s="5" t="s">
         <v>32</v>
       </c>
       <c r="AH1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AI1" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AJ1" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AK1" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AL1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="2" t="s">
+      <c r="AM1" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="2" t="s">
+      <c r="AN1" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="2" t="s">
+      <c r="AO1" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="2" t="s">
+      <c r="AP1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="2" t="s">
+      <c r="AQ1" s="8" t="s">
         <v>42</v>
       </c>
       <c r="AR1" s="2" t="s">
@@ -1632,52 +2538,52 @@
       <c r="AU1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="2" t="s">
+      <c r="AV1" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="2" t="s">
+      <c r="AW1" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" s="2" t="s">
+      <c r="AX1" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" s="2" t="s">
+      <c r="AY1" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" s="2" t="s">
+      <c r="AZ1" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="2" t="s">
+      <c r="BA1" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" s="2" t="s">
+      <c r="BB1" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" s="2" t="s">
+      <c r="BC1" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" s="2" t="s">
+      <c r="BD1" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" s="2" t="s">
+      <c r="BE1" s="3" t="s">
         <v>56</v>
       </c>
       <c r="BF1" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="BG1" s="2" t="s">
+      <c r="BG1" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="BH1" s="2" t="s">
+      <c r="BH1" s="3" t="s">
         <v>59</v>
       </c>
       <c r="BI1" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="BJ1" s="2" t="s">
+      <c r="BJ1" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="BK1" s="2" t="s">
+      <c r="BK1" s="12" t="s">
         <v>62</v>
       </c>
       <c r="BL1" s="2" t="s">
@@ -1698,241 +2604,354 @@
       <c r="BQ1" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="BR1" s="5" t="s">
+      <c r="BR1" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="BS1" s="5" t="s">
+      <c r="BS1" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="BT1" s="6" t="s">
+      <c r="BT1" s="13" t="s">
         <v>71</v>
       </c>
+      <c r="BU1" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="BV1" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="BW1" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="BX1" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="BY1" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="BZ1" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="CA1" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="CB1" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="CC1" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="CD1" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="CE1" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="CF1" s="3" t="s">
+        <v>83</v>
+      </c>
     </row>
-    <row r="2" spans="1:72">
+    <row r="2" spans="1:84">
       <c r="A2" s="2" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>88</v>
+        <v>99</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="AG2" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="AH2" s="3" t="s">
-        <v>105</v>
+        <v>115</v>
+      </c>
+      <c r="AG2" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="AH2" s="2" t="s">
+        <v>117</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="BF2" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="BG2" s="3" t="s">
-        <v>130</v>
+        <v>140</v>
+      </c>
+      <c r="BF2" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="BG2" s="2" t="s">
+        <v>142</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="BJ2" s="3" t="s">
-        <v>133</v>
+        <v>144</v>
+      </c>
+      <c r="BJ2" s="2" t="s">
+        <v>145</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="BM2" s="2" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="BQ2" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="BR2" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="BS2" s="5" t="s">
-        <v>142</v>
+        <v>152</v>
+      </c>
+      <c r="BR2" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="BS2" s="2" t="s">
+        <v>154</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>143</v>
+        <v>155</v>
+      </c>
+      <c r="BU2" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="BV2" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="BW2" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="BX2" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="BY2" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="BZ2" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="CA2" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="CB2" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="CC2" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="CD2" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="CE2" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="CF2" s="2" t="s">
+        <v>167</v>
       </c>
     </row>
-    <row r="5" spans="55:55">
-      <c r="BC5" s="4"/>
+    <row r="3" spans="55:55">
+      <c r="BC3" s="11"/>
     </row>
-    <row r="6" spans="55:55">
-      <c r="BC6" s="4"/>
+    <row r="4" spans="55:55">
+      <c r="BC4" s="11"/>
     </row>
   </sheetData>
+  <dataValidations count="10">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J1">
+      <formula1>"新产品,迭代产品"</formula1>
+    </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W1 AP1">
+      <formula1>1</formula1>
+      <formula2>2958464</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI1 AM1">
+      <formula1>0</formula1>
+      <formula2>99999999999</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ1:AL1 AQ1">
+      <formula1>0</formula1>
+      <formula2>9999999999</formula2>
+    </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN1:AO1">
+      <formula1>32874</formula1>
+      <formula2>2958464</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BK1 BV1:BW1">
+      <formula1>0</formula1>
+      <formula2>999999999999</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BT1:BU1 BX1 CA1:CB1">
+      <formula1>0</formula1>
+      <formula2>99999999999</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BY1">
+      <formula1>0</formula1>
+      <formula2>9999999999999</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BZ1">
+      <formula1>0</formula1>
+      <formula2>9999999999</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CC1">
+      <formula1>0</formula1>
+      <formula2>999999999999</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetail.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetail.xlsx
@@ -1503,12 +1503,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="10.5"/>
       <name val="Helvetica"/>
       <charset val="134"/>
@@ -1517,12 +1511,18 @@
       <sz val="10.5"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10.5"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">

--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetail.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetail.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -385,7 +385,19 @@
     <t>存在侵权风险(是/否)</t>
   </si>
   <si>
-    <t>单位</t>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>单位</t>
+    </r>
   </si>
   <si>
     <t>主要材质</t>
@@ -2469,7 +2481,7 @@
       <c r="X1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Y1" s="3" t="s">
         <v>24</v>
       </c>
       <c r="Z1" s="2" t="s">

--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetail.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetail.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="170">
   <si>
     <t>spu</t>
   </si>
@@ -238,6 +238,9 @@
     </r>
   </si>
   <si>
+    <t>研发团队</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="10"/>
@@ -386,6 +389,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -1106,6 +1116,9 @@
   </si>
   <si>
     <t>{.brandName}</t>
+  </si>
+  <si>
+    <t>{.rdtTeamName}</t>
   </si>
   <si>
     <t>{.productStateName}</t>
@@ -1523,12 +1536,12 @@
       <sz val="10.5"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10.5"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -2367,48 +2380,48 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:CF4"/>
+  <dimension ref="A1:CG4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3"/>
   <cols>
     <col min="4" max="4" width="23.875" customWidth="1"/>
     <col min="9" max="9" width="18.25" customWidth="1"/>
     <col min="13" max="13" width="10.375" customWidth="1"/>
-    <col min="14" max="14" width="16" customWidth="1"/>
-    <col min="20" max="20" width="11.5" customWidth="1"/>
-    <col min="21" max="21" width="13" customWidth="1"/>
-    <col min="22" max="22" width="11" customWidth="1"/>
-    <col min="23" max="23" width="13.25" customWidth="1"/>
-    <col min="24" max="24" width="9.625" customWidth="1"/>
-    <col min="25" max="25" width="10.25" customWidth="1"/>
-    <col min="26" max="26" width="16" customWidth="1"/>
-    <col min="27" max="27" width="14.875" customWidth="1"/>
-    <col min="28" max="28" width="12" customWidth="1"/>
-    <col min="29" max="29" width="12.375" customWidth="1"/>
-    <col min="30" max="30" width="12.125" customWidth="1"/>
-    <col min="31" max="31" width="12.25" customWidth="1"/>
-    <col min="35" max="35" width="12.25" customWidth="1"/>
-    <col min="36" max="36" width="11.125" customWidth="1"/>
-    <col min="37" max="38" width="8.125" customWidth="1"/>
-    <col min="39" max="40" width="9.25" customWidth="1"/>
-    <col min="41" max="42" width="10.875" customWidth="1"/>
-    <col min="50" max="50" width="13.75" customWidth="1"/>
-    <col min="51" max="51" width="11.625" customWidth="1"/>
-    <col min="56" max="56" width="7.125" customWidth="1"/>
-    <col min="57" max="57" width="13" customWidth="1"/>
-    <col min="58" max="58" width="11.125" customWidth="1"/>
-    <col min="59" max="59" width="14.5" customWidth="1"/>
-    <col min="60" max="60" width="11.25" customWidth="1"/>
-    <col min="61" max="61" width="14.125" customWidth="1"/>
-    <col min="62" max="62" width="14.875" customWidth="1"/>
-    <col min="63" max="63" width="12.375" customWidth="1"/>
-    <col min="65" max="65" width="10.75" customWidth="1"/>
-    <col min="66" max="66" width="10.625" customWidth="1"/>
-    <col min="67" max="69" width="11.125" customWidth="1"/>
-    <col min="70" max="71" width="11.125" style="1" customWidth="1"/>
-    <col min="72" max="72" width="11.875" customWidth="1"/>
+    <col min="14" max="15" width="16" customWidth="1"/>
+    <col min="21" max="21" width="11.5" customWidth="1"/>
+    <col min="22" max="22" width="13" customWidth="1"/>
+    <col min="23" max="23" width="11" customWidth="1"/>
+    <col min="24" max="24" width="13.25" customWidth="1"/>
+    <col min="25" max="25" width="9.625" customWidth="1"/>
+    <col min="26" max="26" width="10.25" customWidth="1"/>
+    <col min="27" max="27" width="16" customWidth="1"/>
+    <col min="28" max="28" width="14.875" customWidth="1"/>
+    <col min="29" max="29" width="12" customWidth="1"/>
+    <col min="30" max="30" width="12.375" customWidth="1"/>
+    <col min="31" max="31" width="12.125" customWidth="1"/>
+    <col min="32" max="32" width="12.25" customWidth="1"/>
+    <col min="36" max="36" width="12.25" customWidth="1"/>
+    <col min="37" max="37" width="11.125" customWidth="1"/>
+    <col min="38" max="39" width="8.125" customWidth="1"/>
+    <col min="40" max="41" width="9.25" customWidth="1"/>
+    <col min="42" max="43" width="10.875" customWidth="1"/>
+    <col min="51" max="51" width="13.75" customWidth="1"/>
+    <col min="52" max="52" width="11.625" customWidth="1"/>
+    <col min="57" max="57" width="7.125" customWidth="1"/>
+    <col min="58" max="58" width="13" customWidth="1"/>
+    <col min="59" max="59" width="11.125" customWidth="1"/>
+    <col min="60" max="60" width="14.5" customWidth="1"/>
+    <col min="61" max="61" width="11.25" customWidth="1"/>
+    <col min="62" max="62" width="14.125" customWidth="1"/>
+    <col min="63" max="63" width="14.875" customWidth="1"/>
+    <col min="64" max="64" width="12.375" customWidth="1"/>
+    <col min="66" max="66" width="10.75" customWidth="1"/>
+    <col min="67" max="67" width="10.625" customWidth="1"/>
+    <col min="68" max="70" width="11.125" customWidth="1"/>
+    <col min="71" max="72" width="11.125" style="1" customWidth="1"/>
+    <col min="73" max="73" width="11.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" spans="1:84">
+    <row r="1" ht="24" spans="1:85">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2448,7 +2461,7 @@
       <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="4" t="s">
         <v>13</v>
       </c>
       <c r="O1" s="3" t="s">
@@ -2460,13 +2473,13 @@
       <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="R1" s="3" t="s">
         <v>17</v>
       </c>
       <c r="S1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="5" t="s">
         <v>19</v>
       </c>
       <c r="U1" s="2" t="s">
@@ -2475,22 +2488,22 @@
       <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="X1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Y1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="Z1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="7" t="s">
+      <c r="AA1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="5" t="s">
+      <c r="AB1" s="7" t="s">
         <v>27</v>
       </c>
       <c r="AC1" s="5" t="s">
@@ -2508,10 +2521,10 @@
       <c r="AG1" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AH1" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="8" t="s">
+      <c r="AI1" s="2" t="s">
         <v>34</v>
       </c>
       <c r="AJ1" s="8" t="s">
@@ -2523,10 +2536,10 @@
       <c r="AL1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="9" t="s">
+      <c r="AM1" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="6" t="s">
+      <c r="AN1" s="9" t="s">
         <v>39</v>
       </c>
       <c r="AO1" s="6" t="s">
@@ -2535,10 +2548,10 @@
       <c r="AP1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="8" t="s">
+      <c r="AQ1" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="2" t="s">
+      <c r="AR1" s="8" t="s">
         <v>43</v>
       </c>
       <c r="AS1" s="2" t="s">
@@ -2550,22 +2563,22 @@
       <c r="AU1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="10" t="s">
+      <c r="AV1" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="5" t="s">
+      <c r="AW1" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" s="10" t="s">
+      <c r="AX1" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" s="5" t="s">
+      <c r="AY1" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" s="10" t="s">
+      <c r="AZ1" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="3" t="s">
+      <c r="BA1" s="10" t="s">
         <v>52</v>
       </c>
       <c r="BB1" s="3" t="s">
@@ -2574,31 +2587,31 @@
       <c r="BC1" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" s="6" t="s">
+      <c r="BD1" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" s="3" t="s">
+      <c r="BE1" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" s="2" t="s">
+      <c r="BF1" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="BG1" s="3" t="s">
+      <c r="BG1" s="2" t="s">
         <v>58</v>
       </c>
       <c r="BH1" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="BI1" s="2" t="s">
+      <c r="BI1" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="BJ1" s="5" t="s">
+      <c r="BJ1" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="BK1" s="12" t="s">
+      <c r="BK1" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="BL1" s="2" t="s">
+      <c r="BL1" s="12" t="s">
         <v>63</v>
       </c>
       <c r="BM1" s="2" t="s">
@@ -2622,7 +2635,7 @@
       <c r="BS1" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="BT1" s="13" t="s">
+      <c r="BT1" s="2" t="s">
         <v>71</v>
       </c>
       <c r="BU1" s="13" t="s">
@@ -2649,317 +2662,323 @@
       <c r="CB1" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="CC1" s="8" t="s">
+      <c r="CC1" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="CD1" s="14" t="s">
+      <c r="CD1" s="8" t="s">
         <v>81</v>
       </c>
       <c r="CE1" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="CF1" s="3" t="s">
+      <c r="CF1" s="14" t="s">
         <v>83</v>
       </c>
+      <c r="CG1" s="3" t="s">
+        <v>84</v>
+      </c>
     </row>
-    <row r="2" spans="1:84">
+    <row r="2" spans="1:85">
       <c r="A2" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AY2" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AZ2" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="BA2" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="BB2" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="BC2" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="BD2" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="BE2" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="BF2" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="BG2" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="BH2" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="BI2" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="BJ2" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="BL2" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BM2" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="BN2" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="BO2" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BP2" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="BQ2" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="BR2" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="BS2" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="BT2" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="BU2" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="BW2" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="BX2" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="BY2" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="BZ2" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="CA2" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="CB2" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="CC2" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="CD2" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="CE2" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="CF2" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
+      </c>
+      <c r="CG2" s="2" t="s">
+        <v>169</v>
       </c>
     </row>
-    <row r="3" spans="55:55">
-      <c r="BC3" s="11"/>
+    <row r="3" spans="56:56">
+      <c r="BD3" s="11"/>
     </row>
-    <row r="4" spans="55:55">
-      <c r="BC4" s="11"/>
+    <row r="4" spans="56:56">
+      <c r="BD4" s="11"/>
     </row>
   </sheetData>
   <dataValidations count="10">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J1">
       <formula1>"新产品,迭代产品"</formula1>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W1 AP1">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X1 AQ1">
       <formula1>1</formula1>
       <formula2>2958464</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI1 AM1">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ1 AN1">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ1:AL1 AQ1">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AK1:AM1 AR1">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AN1:AO1">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AO1:AP1">
       <formula1>32874</formula1>
       <formula2>2958464</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BK1 BV1:BW1">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BL1 BW1:BX1">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BT1:BU1 BX1 CA1:CB1">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BU1:BV1 BY1 CB1:CC1">
       <formula1>0</formula1>
       <formula2>99999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BY1">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BZ1">
       <formula1>0</formula1>
       <formula2>9999999999999</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BZ1">
+    <dataValidation type="decimal" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CA1">
       <formula1>0</formula1>
       <formula2>9999999999</formula2>
     </dataValidation>
-    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CC1">
+    <dataValidation type="whole" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="CD1">
       <formula1>0</formula1>
       <formula2>999999999999</formula2>
     </dataValidation>

--- a/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetail.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/productNoSpecDetail.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -217,13 +217,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -242,24 +235,16 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>产品开发状态</t>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BU线</t>
     </r>
   </si>
   <si>
@@ -1121,7 +1106,7 @@
     <t>{.rdtTeamName}</t>
   </si>
   <si>
-    <t>{.productStateName}</t>
+    <t>{.buName}</t>
   </si>
   <si>
     <t>{.grade}</t>
@@ -1528,6 +1513,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10.5"/>
       <name val="Helvetica"/>
       <charset val="134"/>
@@ -1542,12 +1533,6 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -2049,16 +2034,16 @@
     <xf numFmtId="178" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2611,7 +2596,7 @@
       <c r="BK1" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="BL1" s="12" t="s">
+      <c r="BL1" s="11" t="s">
         <v>63</v>
       </c>
       <c r="BM1" s="2" t="s">
@@ -2638,40 +2623,40 @@
       <c r="BT1" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="BU1" s="13" t="s">
+      <c r="BU1" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="BV1" s="13" t="s">
+      <c r="BV1" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="BW1" s="13" t="s">
+      <c r="BW1" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="BX1" s="13" t="s">
+      <c r="BX1" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="BY1" s="13" t="s">
+      <c r="BY1" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="BZ1" s="13" t="s">
+      <c r="BZ1" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="CA1" s="13" t="s">
+      <c r="CA1" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="CB1" s="13" t="s">
+      <c r="CB1" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="CC1" s="13" t="s">
+      <c r="CC1" s="12" t="s">
         <v>80</v>
       </c>
       <c r="CD1" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="CE1" s="14" t="s">
+      <c r="CE1" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="CF1" s="14" t="s">
+      <c r="CF1" s="13" t="s">
         <v>83</v>
       </c>
       <c r="CG1" s="3" t="s">
@@ -2935,11 +2920,11 @@
         <v>169</v>
       </c>
     </row>
-    <row r="3" spans="56:56">
-      <c r="BD3" s="11"/>
+    <row r="3" spans="1:85">
+      <c r="BD3" s="14"/>
     </row>
-    <row r="4" spans="56:56">
-      <c r="BD4" s="11"/>
+    <row r="4" spans="1:85">
+      <c r="BD4" s="14"/>
     </row>
   </sheetData>
   <dataValidations count="10">
